--- a/apps/deep/www/calculators/eastern-corn-belt-plains@v6.xlsx
+++ b/apps/deep/www/calculators/eastern-corn-belt-plains@v6.xlsx
@@ -100,7 +100,7 @@
     <definedName name="in_spring_phab_pct_fast">'DEEP Score'!$E$37</definedName>
     <definedName name="in_spring_phab_xfc_nat">'DEEP Score'!$E$38</definedName>
     <definedName name="in_spring_nid_dams_1mi">'DEEP Score'!$E$39</definedName>
-    <definedName name="site_notes">'DEEP Score'!$A$64</definedName>
+    <definedName name="site_notes">'DEEP Score'!$A$65</definedName>
     <definedName name="meta_assessment_id">'Metadata'!$B$4</definedName>
     <definedName name="meta_assessment_name">'Metadata'!$B$5</definedName>
     <definedName name="meta_version">'Metadata'!$B$6</definedName>
@@ -129,7 +129,7 @@
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -161,8 +161,13 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -215,6 +220,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B45309"/>
+        <bgColor rgb="00B45309"/>
       </patternFill>
     </fill>
   </fills>
@@ -509,10 +520,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1476,6 +1490,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1499,78 +1514,85 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>This workbook scores one detailed assessment. It carries the assessment's metrics and their reference curves, and it scores exactly as the DEEP web application does.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Reference condition. Reference curves are built from least-disturbed stations chosen by a fixed landscape-pressure screen. Where this ecoregion has too few, comparable stations of its Level II and then its Level I ecoregion are used, and a metric with no defensible pool is not scored. Landscape pressure metrics are scored on fixed criteria.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>1. On the DEEP Score sheet, fill the site block and type each metric's measured value in its orange cell, in the units shown.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2. Where a metric has several curve sets, choose the set that fits the reach from the list beside the value. Left alone, the default set applies.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>3. Leave a value blank when the metric does not apply. It drops out of the score.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>4. A metric that serves more than one function is entered once. The grey cells repeat it.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>5. The index of each metric (0 to 1) is read from its reference curve. The function score is the mean index of the function's metrics times 15.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>6. The outcome sub-indices weigh each function's score by its direct or indirect contribution, and the Ecosystem Condition Index is the mean of the three.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Condition classes. Index at or below 0.39 Non-Functioning, at or below 0.69 Functioning At-Risk, above Functioning. Function score at or below 5 Non-Functioning, at or below 10 Functioning At-Risk, above Functioning.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Sheets. DEEP Score (entries and results), Metrics (the interpolation of every metric), Reference (curves, curve sets, classes), Metadata (assessment identity).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>The sheets are protected against accidental edits. The password is deep.</t>
         </is>
@@ -1579,16 +1601,25 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1617,1082 +1648,1084 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Version 6 | StreamCurves reference-curve development</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Version 6 | Preliminary | StreamCurves reference-curve development</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Stream or site</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Reach ID</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Assessor(s)</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Curve set</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Function score (0 to 15)</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Hydrology</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Catchment hydrology</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Agriculture, crop and hay</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="15" t="inlineStr"/>
-      <c r="G12" s="16">
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="17">
         <f>IF('Metrics'!$V$5="","",'Metrics'!$V$5)</f>
         <v/>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="18">
         <f>IF('Results'!$B$4="","",'Results'!$B$4)</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="19">
         <f>IF('DEEP Score'!$H$12="","",IF('DEEP Score'!$H$12&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$12&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n"/>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Impervious surface</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="24" t="inlineStr"/>
-      <c r="G13" s="25">
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="25" t="inlineStr"/>
+      <c r="G13" s="26">
         <f>IF('Metrics'!$V$6="","",'Metrics'!$V$6)</f>
         <v/>
       </c>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="26" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="27" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Hydrology</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Surface water storage</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>Wetland</t>
         </is>
       </c>
-      <c r="D14" s="30" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E14" s="31" t="n"/>
-      <c r="F14" s="32" t="inlineStr"/>
-      <c r="G14" s="33">
+      <c r="E14" s="32" t="n"/>
+      <c r="F14" s="33" t="inlineStr"/>
+      <c r="G14" s="34">
         <f>IF('Metrics'!$V$7="","",'Metrics'!$V$7)</f>
         <v/>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="35">
         <f>IF('Results'!$B$5="","",'Results'!$B$5)</f>
         <v/>
       </c>
-      <c r="I14" s="35">
+      <c r="I14" s="36">
         <f>IF('DEEP Score'!$H$14="","",IF('DEEP Score'!$H$14&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$14&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Hydrology</t>
         </is>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Reach inflow</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>Road density</t>
         </is>
       </c>
-      <c r="D15" s="30" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>km/sq km</t>
         </is>
       </c>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="32" t="inlineStr"/>
-      <c r="G15" s="33">
+      <c r="E15" s="32" t="n"/>
+      <c r="F15" s="33" t="inlineStr"/>
+      <c r="G15" s="34">
         <f>IF('Metrics'!$V$8="","",'Metrics'!$V$8)</f>
         <v/>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="35">
         <f>IF('Results'!$B$6="","",'Results'!$B$6)</f>
         <v/>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="36">
         <f>IF('DEEP Score'!$H$15="","",IF('DEEP Score'!$H$15&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$15&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Hydrology</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Streamflow regime</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Base flow index</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="15" t="inlineStr"/>
-      <c r="G16" s="16">
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="16" t="inlineStr"/>
+      <c r="G16" s="17">
         <f>IF('Metrics'!$V$9="","",'Metrics'!$V$9)</f>
         <v/>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="18">
         <f>IF('Results'!$B$7="","",'Results'!$B$7)</f>
         <v/>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="19">
         <f>IF('DEEP Score'!$H$16="","",IF('DEEP Score'!$H$16&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$16&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n"/>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="A17" s="20" t="n"/>
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Degree of regulation</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E17" s="23" t="n"/>
-      <c r="F17" s="24" t="inlineStr"/>
-      <c r="G17" s="25">
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="25" t="inlineStr"/>
+      <c r="G17" s="26">
         <f>IF('Metrics'!$V$10="","",'Metrics'!$V$10)</f>
         <v/>
       </c>
-      <c r="H17" s="20" t="n"/>
-      <c r="I17" s="26" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="27" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>Hydraulics</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Low flow and baseflow dynamics</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Bankfull width:depth ratio</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="15" t="inlineStr"/>
-      <c r="G18" s="16">
+      <c r="D18" s="14" t="inlineStr"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="16" t="inlineStr"/>
+      <c r="G18" s="17">
         <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
         <v/>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="18">
         <f>IF('Results'!$B$8="","",'Results'!$B$8)</f>
         <v/>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="19">
         <f>IF('DEEP Score'!$H$18="","",IF('DEEP Score'!$H$18&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$18&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="n"/>
-      <c r="B19" s="38" t="n"/>
-      <c r="C19" s="39" t="inlineStr">
+      <c r="A19" s="38" t="n"/>
+      <c r="B19" s="39" t="n"/>
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>Residual pool depth</t>
         </is>
       </c>
-      <c r="D19" s="40" t="inlineStr">
+      <c r="D19" s="41" t="inlineStr">
         <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="E19" s="41" t="n"/>
-      <c r="F19" s="42" t="inlineStr"/>
-      <c r="G19" s="43">
+      <c r="E19" s="42" t="n"/>
+      <c r="F19" s="43" t="inlineStr"/>
+      <c r="G19" s="44">
         <f>IF('Metrics'!$V$12="","",'Metrics'!$V$12)</f>
         <v/>
       </c>
-      <c r="H19" s="38" t="n"/>
-      <c r="I19" s="44" t="n"/>
+      <c r="H19" s="39" t="n"/>
+      <c r="I19" s="45" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="n"/>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="A20" s="20" t="n"/>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>Base flow index</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="46">
         <f>IF('DEEP Score'!$E$16="","",'DEEP Score'!$E$16)</f>
         <v/>
       </c>
-      <c r="F20" s="46" t="inlineStr"/>
-      <c r="G20" s="25">
+      <c r="F20" s="47" t="inlineStr"/>
+      <c r="G20" s="26">
         <f>IF('Metrics'!$V$9="","",'Metrics'!$V$9)</f>
         <v/>
       </c>
-      <c r="H20" s="20" t="n"/>
-      <c r="I20" s="26" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="27" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="47" t="inlineStr">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t>Hydraulics</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>High flow dynamics</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>Impervious surface</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="49">
         <f>IF('DEEP Score'!$E$13="","",'DEEP Score'!$E$13)</f>
         <v/>
       </c>
-      <c r="F21" s="49" t="inlineStr"/>
-      <c r="G21" s="33">
+      <c r="F21" s="50" t="inlineStr"/>
+      <c r="G21" s="34">
         <f>IF('Metrics'!$V$6="","",'Metrics'!$V$6)</f>
         <v/>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="35">
         <f>IF('Results'!$B$9="","",'Results'!$B$9)</f>
         <v/>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="36">
         <f>IF('DEEP Score'!$H$21="","",IF('DEEP Score'!$H$21&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$21&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>Hydraulics</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Floodplain connectivity</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Bankfull width:depth ratio</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr"/>
-      <c r="E22" s="50">
+      <c r="D22" s="14" t="inlineStr"/>
+      <c r="E22" s="51">
         <f>IF('DEEP Score'!$E$18="","",'DEEP Score'!$E$18)</f>
         <v/>
       </c>
-      <c r="F22" s="51" t="inlineStr"/>
-      <c r="G22" s="16">
+      <c r="F22" s="52" t="inlineStr"/>
+      <c r="G22" s="17">
         <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
         <v/>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="18">
         <f>IF('Results'!$B$10="","",'Results'!$B$10)</f>
         <v/>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="19">
         <f>IF('DEEP Score'!$H$22="","",IF('DEEP Score'!$H$22&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$22&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="n"/>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="n"/>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>Bankfull height above channel</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E23" s="23" t="n"/>
-      <c r="F23" s="24" t="inlineStr"/>
-      <c r="G23" s="25">
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="25" t="inlineStr"/>
+      <c r="G23" s="26">
         <f>IF('Metrics'!$V$13="","",'Metrics'!$V$13)</f>
         <v/>
       </c>
-      <c r="H23" s="20" t="n"/>
-      <c r="I23" s="26" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="27" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>Hydraulics</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Hyporheic connectivity</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Sand + fines</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="15" t="inlineStr"/>
-      <c r="G24" s="16">
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="16" t="inlineStr"/>
+      <c r="G24" s="17">
         <f>IF('Metrics'!$V$14="","",'Metrics'!$V$14)</f>
         <v/>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="18">
         <f>IF('Results'!$B$11="","",'Results'!$B$11)</f>
         <v/>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="19">
         <f>IF('DEEP Score'!$H$24="","",IF('DEEP Score'!$H$24&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$24&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="n"/>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="A25" s="20" t="n"/>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>Embeddedness</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="24" t="inlineStr"/>
-      <c r="G25" s="25">
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="25" t="inlineStr"/>
+      <c r="G25" s="26">
         <f>IF('Metrics'!$V$15="","",'Metrics'!$V$15)</f>
         <v/>
       </c>
-      <c r="H25" s="20" t="n"/>
-      <c r="I25" s="26" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="27" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="inlineStr">
+      <c r="A26" s="53" t="inlineStr">
         <is>
           <t>Geomorphology</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Channel evolution</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Bankfull width:depth ratio</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr"/>
-      <c r="E26" s="50">
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="51">
         <f>IF('DEEP Score'!$E$18="","",'DEEP Score'!$E$18)</f>
         <v/>
       </c>
-      <c r="F26" s="51" t="inlineStr"/>
-      <c r="G26" s="16">
+      <c r="F26" s="52" t="inlineStr"/>
+      <c r="G26" s="17">
         <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
         <v/>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="18">
         <f>IF('Results'!$B$12="","",'Results'!$B$12)</f>
         <v/>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="19">
         <f>IF('DEEP Score'!$H$26="","",IF('DEEP Score'!$H$26&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$26&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="A27" s="20" t="n"/>
+      <c r="B27" s="21" t="n"/>
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>Bankfull height above channel</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E27" s="45">
+      <c r="E27" s="46">
         <f>IF('DEEP Score'!$E$23="","",'DEEP Score'!$E$23)</f>
         <v/>
       </c>
-      <c r="F27" s="46" t="inlineStr"/>
-      <c r="G27" s="25">
+      <c r="F27" s="47" t="inlineStr"/>
+      <c r="G27" s="26">
         <f>IF('Metrics'!$V$13="","",'Metrics'!$V$13)</f>
         <v/>
       </c>
-      <c r="H27" s="20" t="n"/>
-      <c r="I27" s="26" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="27" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="52" t="inlineStr">
+      <c r="A28" s="53" t="inlineStr">
         <is>
           <t>Geomorphology</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Channel and floodplain dynamics</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Sinuosity</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr"/>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="15" t="inlineStr"/>
-      <c r="G28" s="16">
+      <c r="D28" s="14" t="inlineStr"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="16" t="inlineStr"/>
+      <c r="G28" s="17">
         <f>IF('Metrics'!$V$16="","",'Metrics'!$V$16)</f>
         <v/>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="18">
         <f>IF('Results'!$B$13="","",'Results'!$B$13)</f>
         <v/>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="19">
         <f>IF('DEEP Score'!$H$28="","",IF('DEEP Score'!$H$28&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$28&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="A29" s="20" t="n"/>
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>Bank angle</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>degrees</t>
         </is>
       </c>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="24" t="inlineStr"/>
-      <c r="G29" s="25">
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="25" t="inlineStr"/>
+      <c r="G29" s="26">
         <f>IF('Metrics'!$V$17="","",'Metrics'!$V$17)</f>
         <v/>
       </c>
-      <c r="H29" s="20" t="n"/>
-      <c r="I29" s="26" t="n"/>
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="27" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="52" t="inlineStr">
+      <c r="A30" s="53" t="inlineStr">
         <is>
           <t>Geomorphology</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Sediment continuity</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>Relative bed stability</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>log</t>
         </is>
       </c>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="15" t="inlineStr"/>
-      <c r="G30" s="16">
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="16" t="inlineStr"/>
+      <c r="G30" s="17">
         <f>IF('Metrics'!$V$18="","",'Metrics'!$V$18)</f>
         <v/>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="18">
         <f>IF('Results'!$B$14="","",'Results'!$B$14)</f>
         <v/>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="19">
         <f>IF('DEEP Score'!$H$30="","",IF('DEEP Score'!$H$30&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$30&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="n"/>
-      <c r="B31" s="20" t="n"/>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="A31" s="20" t="n"/>
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>Sand + fines</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E31" s="45">
+      <c r="E31" s="46">
         <f>IF('DEEP Score'!$E$24="","",'DEEP Score'!$E$24)</f>
         <v/>
       </c>
-      <c r="F31" s="46" t="inlineStr"/>
-      <c r="G31" s="25">
+      <c r="F31" s="47" t="inlineStr"/>
+      <c r="G31" s="26">
         <f>IF('Metrics'!$V$14="","",'Metrics'!$V$14)</f>
         <v/>
       </c>
-      <c r="H31" s="20" t="n"/>
-      <c r="I31" s="26" t="n"/>
+      <c r="H31" s="21" t="n"/>
+      <c r="I31" s="27" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="52" t="inlineStr">
+      <c r="A32" s="53" t="inlineStr">
         <is>
           <t>Geomorphology</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Bed composition and bedform dynamics</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Substrate size</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>log mm</t>
         </is>
       </c>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="15" t="inlineStr"/>
-      <c r="G32" s="16">
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="16" t="inlineStr"/>
+      <c r="G32" s="17">
         <f>IF('Metrics'!$V$19="","",'Metrics'!$V$19)</f>
         <v/>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="18">
         <f>IF('Results'!$B$15="","",'Results'!$B$15)</f>
         <v/>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="19">
         <f>IF('DEEP Score'!$H$32="","",IF('DEEP Score'!$H$32&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$32&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="n"/>
-      <c r="B33" s="38" t="n"/>
-      <c r="C33" s="39" t="inlineStr">
+      <c r="A33" s="38" t="n"/>
+      <c r="B33" s="39" t="n"/>
+      <c r="C33" s="40" t="inlineStr">
         <is>
           <t>Large wood volume</t>
         </is>
       </c>
-      <c r="D33" s="40" t="inlineStr">
+      <c r="D33" s="41" t="inlineStr">
         <is>
           <t>m3/100m</t>
         </is>
       </c>
-      <c r="E33" s="41" t="n"/>
-      <c r="F33" s="42" t="inlineStr"/>
-      <c r="G33" s="43">
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="43" t="inlineStr"/>
+      <c r="G33" s="44">
         <f>IF('Metrics'!$V$20="","",'Metrics'!$V$20)</f>
         <v/>
       </c>
-      <c r="H33" s="38" t="n"/>
-      <c r="I33" s="44" t="n"/>
+      <c r="H33" s="39" t="n"/>
+      <c r="I33" s="45" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="n"/>
-      <c r="B34" s="20" t="n"/>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="A34" s="20" t="n"/>
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>Embeddedness</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E34" s="45">
+      <c r="E34" s="46">
         <f>IF('DEEP Score'!$E$25="","",'DEEP Score'!$E$25)</f>
         <v/>
       </c>
-      <c r="F34" s="46" t="inlineStr"/>
-      <c r="G34" s="25">
+      <c r="F34" s="47" t="inlineStr"/>
+      <c r="G34" s="26">
         <f>IF('Metrics'!$V$15="","",'Metrics'!$V$15)</f>
         <v/>
       </c>
-      <c r="H34" s="20" t="n"/>
-      <c r="I34" s="26" t="n"/>
+      <c r="H34" s="21" t="n"/>
+      <c r="I34" s="27" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="53" t="inlineStr">
+      <c r="A35" s="54" t="inlineStr">
         <is>
           <t>Physicochemistry</t>
         </is>
       </c>
-      <c r="B35" s="28" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>Light &amp; thermal regime</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="C35" s="30" t="inlineStr">
         <is>
           <t>Canopy density, mid-channel</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="32" t="inlineStr"/>
-      <c r="G35" s="33">
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="33" t="inlineStr"/>
+      <c r="G35" s="34">
         <f>IF('Metrics'!$V$21="","",'Metrics'!$V$21)</f>
         <v/>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="35">
         <f>IF('Results'!$B$16="","",'Results'!$B$16)</f>
         <v/>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <f>IF('DEEP Score'!$H$35="","",IF('DEEP Score'!$H$35&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$35&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="53" t="inlineStr">
+      <c r="A36" s="54" t="inlineStr">
         <is>
           <t>Physicochemistry</t>
         </is>
       </c>
-      <c r="B36" s="28" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>Carbon processing</t>
         </is>
       </c>
-      <c r="C36" s="29" t="inlineStr">
+      <c r="C36" s="30" t="inlineStr">
         <is>
           <t>Riparian veg cover, woody</t>
         </is>
       </c>
-      <c r="D36" s="30" t="inlineStr">
+      <c r="D36" s="31" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="32" t="inlineStr"/>
-      <c r="G36" s="33">
+      <c r="E36" s="32" t="n"/>
+      <c r="F36" s="33" t="inlineStr"/>
+      <c r="G36" s="34">
         <f>IF('Metrics'!$V$22="","",'Metrics'!$V$22)</f>
         <v/>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="35">
         <f>IF('Results'!$B$17="","",'Results'!$B$17)</f>
         <v/>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="36">
         <f>IF('DEEP Score'!$H$36="","",IF('DEEP Score'!$H$36&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$36&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="54" t="inlineStr">
+      <c r="A37" s="55" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Habitat provision</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>Fast-water / riffle habitat</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="15" t="inlineStr"/>
-      <c r="G37" s="16">
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="16" t="inlineStr"/>
+      <c r="G37" s="17">
         <f>IF('Metrics'!$V$23="","",'Metrics'!$V$23)</f>
         <v/>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="18">
         <f>IF('Results'!$B$18="","",'Results'!$B$18)</f>
         <v/>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="19">
         <f>IF('DEEP Score'!$H$37="","",IF('DEEP Score'!$H$37&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$37&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="n"/>
-      <c r="B38" s="20" t="n"/>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="A38" s="20" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>Natural fish cover</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="E38" s="23" t="n"/>
-      <c r="F38" s="24" t="inlineStr"/>
-      <c r="G38" s="25">
+      <c r="E38" s="24" t="n"/>
+      <c r="F38" s="25" t="inlineStr"/>
+      <c r="G38" s="26">
         <f>IF('Metrics'!$V$24="","",'Metrics'!$V$24)</f>
         <v/>
       </c>
-      <c r="H38" s="20" t="n"/>
-      <c r="I38" s="26" t="n"/>
+      <c r="H38" s="21" t="n"/>
+      <c r="I38" s="27" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="55" t="inlineStr">
+      <c r="A39" s="56" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B39" s="28" t="inlineStr">
+      <c r="B39" s="29" t="inlineStr">
         <is>
           <t>Watershed connectivity</t>
         </is>
       </c>
-      <c r="C39" s="29" t="inlineStr">
+      <c r="C39" s="30" t="inlineStr">
         <is>
           <t>Mapped dams within one mile</t>
         </is>
       </c>
-      <c r="D39" s="30" t="inlineStr">
+      <c r="D39" s="31" t="inlineStr">
         <is>
           <t>dams</t>
         </is>
       </c>
-      <c r="E39" s="31" t="n"/>
-      <c r="F39" s="32" t="inlineStr"/>
-      <c r="G39" s="33">
+      <c r="E39" s="32" t="n"/>
+      <c r="F39" s="33" t="inlineStr"/>
+      <c r="G39" s="34">
         <f>IF('Metrics'!$V$25="","",'Metrics'!$V$25)</f>
         <v/>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="35">
         <f>IF('Results'!$B$19="","",'Results'!$B$19)</f>
         <v/>
       </c>
-      <c r="I39" s="35">
+      <c r="I39" s="36">
         <f>IF('DEEP Score'!$H$39="","",IF('DEEP Score'!$H$39&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$39&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="56" t="inlineStr">
+      <c r="A41" s="57" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Sub-index (0 to 1)</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="57" t="inlineStr">
+      <c r="A43" s="58" t="inlineStr">
         <is>
           <t>Physical</t>
         </is>
       </c>
-      <c r="B43" s="58">
+      <c r="B43" s="59">
         <f>'Results'!$B$22</f>
         <v/>
       </c>
-      <c r="C43" s="40">
+      <c r="C43" s="41">
         <f>IF('DEEP Score'!$B$43&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$43&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="57" t="inlineStr">
+      <c r="A44" s="58" t="inlineStr">
         <is>
           <t>Chemical</t>
         </is>
       </c>
-      <c r="B44" s="58">
+      <c r="B44" s="59">
         <f>'Results'!$B$23</f>
         <v/>
       </c>
-      <c r="C44" s="40">
+      <c r="C44" s="41">
         <f>IF('DEEP Score'!$B$44&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$44&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="57" t="inlineStr">
+      <c r="A45" s="58" t="inlineStr">
         <is>
           <t>Biological</t>
         </is>
       </c>
-      <c r="B45" s="58">
+      <c r="B45" s="59">
         <f>'Results'!$B$24</f>
         <v/>
       </c>
-      <c r="C45" s="40">
+      <c r="C45" s="41">
         <f>IF('DEEP Score'!$B$45&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$45&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="59" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>Ecosystem Condition Index</t>
         </is>
       </c>
-      <c r="B46" s="60">
+      <c r="B46" s="61">
         <f>'Results'!$B$25</f>
         <v/>
       </c>
-      <c r="C46" s="40">
+      <c r="C46" s="41">
         <f>IF('DEEP Score'!$B$46&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$46&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>This index is computed over the 16 functions this assessment scores. 4 of the 20 STAF functions are not assessed, so it is not comparable with a full-framework index and no condition class is claimed for the assessment as a whole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Functions with a score: </t>
         </is>
       </c>
-      <c r="B47" s="4">
+      <c r="B48" s="5">
         <f>COUNT('Results'!$B$4:$B$19)&amp;" of 16"</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>This assessment covers 16 of 20 STAF functions (4 documented exclusions).</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="61" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="62" t="inlineStr">
         <is>
           <t>Withheld for insufficient reference support (not scored)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>EPT taxa richness</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Community dynamics</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Shannon diversity (H')</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
+          <t>EPT taxa richness</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Community dynamics</t>
         </is>
@@ -2701,10 +2734,10 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tolerant individuals (%) ~ HBI</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
+          <t>Shannon diversity (H')</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Community dynamics</t>
         </is>
@@ -2713,175 +2746,187 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Benthic total taxa richness</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Population support</t>
+          <t>Tolerant individuals (%) ~ HBI</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Community dynamics</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Chlorophyll a</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Light and thermal regime</t>
+          <t>Benthic total taxa richness</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Population support</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Specific conductivity</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Water and soil quality</t>
+          <t>Chlorophyll a</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Light and thermal regime</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dissolved nitrogen</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Nutrient cycling</t>
+          <t>Specific conductivity</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Water and soil quality</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Water and soil quality</t>
+          <t>Dissolved nitrogen</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Nutrient cycling</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Total phosphorus</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Nutrient cycling</t>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Water and soil quality</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Turbidity</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Water and soil quality</t>
+          <t>Total phosphorus</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Nutrient cycling</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Turbidity</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Water and soil quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>Native fish taxa richness</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Population support</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="62" t="n"/>
-      <c r="B64" s="63" t="n"/>
-      <c r="C64" s="63" t="n"/>
-      <c r="D64" s="63" t="n"/>
-      <c r="E64" s="63" t="n"/>
-      <c r="F64" s="63" t="n"/>
-      <c r="G64" s="63" t="n"/>
-      <c r="H64" s="63" t="n"/>
-      <c r="I64" s="64" t="n"/>
-    </row>
     <row r="65">
-      <c r="A65" s="65" t="n"/>
-      <c r="B65" s="66" t="n"/>
-      <c r="C65" s="66" t="n"/>
-      <c r="D65" s="66" t="n"/>
-      <c r="E65" s="66" t="n"/>
-      <c r="F65" s="66" t="n"/>
-      <c r="G65" s="66" t="n"/>
-      <c r="H65" s="66" t="n"/>
-      <c r="I65" s="67" t="n"/>
+      <c r="A65" s="63" t="n"/>
+      <c r="B65" s="64" t="n"/>
+      <c r="C65" s="64" t="n"/>
+      <c r="D65" s="64" t="n"/>
+      <c r="E65" s="64" t="n"/>
+      <c r="F65" s="64" t="n"/>
+      <c r="G65" s="64" t="n"/>
+      <c r="H65" s="64" t="n"/>
+      <c r="I65" s="65" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="65" t="n"/>
-      <c r="B66" s="66" t="n"/>
-      <c r="C66" s="66" t="n"/>
-      <c r="D66" s="66" t="n"/>
-      <c r="E66" s="66" t="n"/>
-      <c r="F66" s="66" t="n"/>
-      <c r="G66" s="66" t="n"/>
-      <c r="H66" s="66" t="n"/>
-      <c r="I66" s="67" t="n"/>
+      <c r="A66" s="66" t="n"/>
+      <c r="B66" s="67" t="n"/>
+      <c r="C66" s="67" t="n"/>
+      <c r="D66" s="67" t="n"/>
+      <c r="E66" s="67" t="n"/>
+      <c r="F66" s="67" t="n"/>
+      <c r="G66" s="67" t="n"/>
+      <c r="H66" s="67" t="n"/>
+      <c r="I66" s="68" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="65" t="n"/>
-      <c r="B67" s="66" t="n"/>
-      <c r="C67" s="66" t="n"/>
-      <c r="D67" s="66" t="n"/>
-      <c r="E67" s="66" t="n"/>
-      <c r="F67" s="66" t="n"/>
-      <c r="G67" s="66" t="n"/>
-      <c r="H67" s="66" t="n"/>
-      <c r="I67" s="67" t="n"/>
+      <c r="A67" s="66" t="n"/>
+      <c r="B67" s="67" t="n"/>
+      <c r="C67" s="67" t="n"/>
+      <c r="D67" s="67" t="n"/>
+      <c r="E67" s="67" t="n"/>
+      <c r="F67" s="67" t="n"/>
+      <c r="G67" s="67" t="n"/>
+      <c r="H67" s="67" t="n"/>
+      <c r="I67" s="68" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="65" t="n"/>
-      <c r="B68" s="66" t="n"/>
-      <c r="C68" s="66" t="n"/>
-      <c r="D68" s="66" t="n"/>
-      <c r="E68" s="66" t="n"/>
-      <c r="F68" s="66" t="n"/>
-      <c r="G68" s="66" t="n"/>
-      <c r="H68" s="66" t="n"/>
-      <c r="I68" s="67" t="n"/>
+      <c r="A68" s="66" t="n"/>
+      <c r="B68" s="67" t="n"/>
+      <c r="C68" s="67" t="n"/>
+      <c r="D68" s="67" t="n"/>
+      <c r="E68" s="67" t="n"/>
+      <c r="F68" s="67" t="n"/>
+      <c r="G68" s="67" t="n"/>
+      <c r="H68" s="67" t="n"/>
+      <c r="I68" s="68" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="68" t="n"/>
-      <c r="B69" s="69" t="n"/>
-      <c r="C69" s="69" t="n"/>
-      <c r="D69" s="69" t="n"/>
-      <c r="E69" s="69" t="n"/>
-      <c r="F69" s="69" t="n"/>
-      <c r="G69" s="69" t="n"/>
-      <c r="H69" s="69" t="n"/>
-      <c r="I69" s="70" t="n"/>
+      <c r="A69" s="66" t="n"/>
+      <c r="B69" s="67" t="n"/>
+      <c r="C69" s="67" t="n"/>
+      <c r="D69" s="67" t="n"/>
+      <c r="E69" s="67" t="n"/>
+      <c r="F69" s="67" t="n"/>
+      <c r="G69" s="67" t="n"/>
+      <c r="H69" s="67" t="n"/>
+      <c r="I69" s="68" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="69" t="n"/>
+      <c r="B70" s="70" t="n"/>
+      <c r="C70" s="70" t="n"/>
+      <c r="D70" s="70" t="n"/>
+      <c r="E70" s="70" t="n"/>
+      <c r="F70" s="70" t="n"/>
+      <c r="G70" s="70" t="n"/>
+      <c r="H70" s="70" t="n"/>
+      <c r="I70" s="71" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
-  <mergeCells count="46">
+  <mergeCells count="48">
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="I30:I31"/>
@@ -2896,6 +2941,7 @@
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="I28:I29"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="I12:I13"/>
@@ -2905,11 +2951,11 @@
     <mergeCell ref="I37:I38"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B32:B34"/>
+    <mergeCell ref="A4:I4"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="I24:I25"/>
     <mergeCell ref="B37:B38"/>
-    <mergeCell ref="A64:I69"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="H16:H17"/>
@@ -2924,6 +2970,7 @@
     <mergeCell ref="H30:H31"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A65:I70"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="A18:A20"/>
@@ -2963,6 +3010,14 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -2970,6 +3025,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2982,2051 +3038,2070 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="71" t="inlineStr">
+      <c r="A1" s="72" t="inlineStr">
         <is>
           <t>Metric indices</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>One row per metric. The value and the curve set come from the DEEP Score sheet, the knots from the Reference sheet, and the index is DEEP's piecewise-linear interpolation.</t>
         </is>
       </c>
     </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Curve set in use</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Curve key</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Curve row</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>x3</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>x4</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>x5</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>x6</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>x7</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>x8</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>y1</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>y2</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>y3</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>y4</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>y5</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="S4" s="6" t="inlineStr">
         <is>
           <t>y6</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="T4" s="6" t="inlineStr">
         <is>
           <t>y7</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="U4" s="6" t="inlineStr">
         <is>
           <t>y8</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>Agriculture, crop and hay</t>
         </is>
       </c>
-      <c r="B5" s="72">
+      <c r="B5" s="73">
         <f>IF('DEEP Score'!$E$12="","",'DEEP Score'!$E$12)</f>
         <v/>
       </c>
-      <c r="C5" s="72">
+      <c r="C5" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D5" s="72">
+      <c r="D5" s="73">
         <f>"spring_pctag2019ws|"&amp;'Metrics'!$C$5</f>
         <v/>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$5,curve_key,0),MATCH("spring_pctag2019ws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F5" s="72">
+      <c r="F5" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="G5" s="72">
+      <c r="G5" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="H5" s="72">
+      <c r="H5" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="I5" s="72">
+      <c r="I5" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="J5" s="72">
+      <c r="J5" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="K5" s="72">
+      <c r="K5" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="L5" s="72">
+      <c r="L5" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="M5" s="72">
+      <c r="M5" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="N5" s="72">
+      <c r="N5" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="O5" s="72">
+      <c r="O5" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="P5" s="72">
+      <c r="P5" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="Q5" s="72">
+      <c r="Q5" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="R5" s="72">
+      <c r="R5" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="S5" s="72">
+      <c r="S5" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="T5" s="72">
+      <c r="T5" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="U5" s="72">
+      <c r="U5" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="V5" s="73">
+      <c r="V5" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$5),MAX(0,MIN(1,IF('Metrics'!$B$5&lt;='Metrics'!$F$5,'Metrics'!$N$5,IF('Metrics'!$B$5&gt;='Metrics'!$M$5,'Metrics'!$U$5,IF('Metrics'!$B$5&lt;='Metrics'!$G$5,IF('Metrics'!$G$5-'Metrics'!$F$5&lt;=0,'Metrics'!$O$5,'Metrics'!$N$5+('Metrics'!$B$5-'Metrics'!$F$5)/('Metrics'!$G$5-'Metrics'!$F$5)*('Metrics'!$O$5-'Metrics'!$N$5)),IF('Metrics'!$B$5&lt;='Metrics'!$H$5,IF('Metrics'!$H$5-'Metrics'!$G$5&lt;=0,'Metrics'!$P$5,'Metrics'!$O$5+('Metrics'!$B$5-'Metrics'!$G$5)/('Metrics'!$H$5-'Metrics'!$G$5)*('Metrics'!$P$5-'Metrics'!$O$5)),IF('Metrics'!$B$5&lt;='Metrics'!$I$5,IF('Metrics'!$I$5-'Metrics'!$H$5&lt;=0,'Metrics'!$Q$5,'Metrics'!$P$5+('Metrics'!$B$5-'Metrics'!$H$5)/('Metrics'!$I$5-'Metrics'!$H$5)*('Metrics'!$Q$5-'Metrics'!$P$5)),IF('Metrics'!$B$5&lt;='Metrics'!$J$5,IF('Metrics'!$J$5-'Metrics'!$I$5&lt;=0,'Metrics'!$R$5,'Metrics'!$Q$5+('Metrics'!$B$5-'Metrics'!$I$5)/('Metrics'!$J$5-'Metrics'!$I$5)*('Metrics'!$R$5-'Metrics'!$Q$5)),IF('Metrics'!$B$5&lt;='Metrics'!$K$5,IF('Metrics'!$K$5-'Metrics'!$J$5&lt;=0,'Metrics'!$S$5,'Metrics'!$R$5+('Metrics'!$B$5-'Metrics'!$J$5)/('Metrics'!$K$5-'Metrics'!$J$5)*('Metrics'!$S$5-'Metrics'!$R$5)),IF('Metrics'!$B$5&lt;='Metrics'!$L$5,IF('Metrics'!$L$5-'Metrics'!$K$5&lt;=0,'Metrics'!$T$5,'Metrics'!$S$5+('Metrics'!$B$5-'Metrics'!$K$5)/('Metrics'!$L$5-'Metrics'!$K$5)*('Metrics'!$T$5-'Metrics'!$S$5)),IF('Metrics'!$M$5-'Metrics'!$L$5&lt;=0,'Metrics'!$U$5,'Metrics'!$T$5+('Metrics'!$B$5-'Metrics'!$L$5)/('Metrics'!$M$5-'Metrics'!$L$5)*('Metrics'!$U$5-'Metrics'!$T$5)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>Impervious surface</t>
         </is>
       </c>
-      <c r="B6" s="72">
+      <c r="B6" s="73">
         <f>IF('DEEP Score'!$E$13="","",'DEEP Score'!$E$13)</f>
         <v/>
       </c>
-      <c r="C6" s="72">
+      <c r="C6" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="73">
         <f>"spring_pctimp2019ws|"&amp;'Metrics'!$C$6</f>
         <v/>
       </c>
-      <c r="E6" s="72">
+      <c r="E6" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$6,curve_key,0),MATCH("spring_pctimp2019ws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F6" s="72">
+      <c r="F6" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="G6" s="72">
+      <c r="G6" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="H6" s="72">
+      <c r="H6" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="I6" s="72">
+      <c r="I6" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="J6" s="72">
+      <c r="J6" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="K6" s="72">
+      <c r="K6" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="L6" s="72">
+      <c r="L6" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="M6" s="72">
+      <c r="M6" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="N6" s="72">
+      <c r="N6" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="O6" s="72">
+      <c r="O6" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="P6" s="72">
+      <c r="P6" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="Q6" s="72">
+      <c r="Q6" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="R6" s="72">
+      <c r="R6" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="S6" s="72">
+      <c r="S6" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="T6" s="72">
+      <c r="T6" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="U6" s="72">
+      <c r="U6" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="V6" s="73">
+      <c r="V6" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$6),MAX(0,MIN(1,IF('Metrics'!$B$6&lt;='Metrics'!$F$6,'Metrics'!$N$6,IF('Metrics'!$B$6&gt;='Metrics'!$M$6,'Metrics'!$U$6,IF('Metrics'!$B$6&lt;='Metrics'!$G$6,IF('Metrics'!$G$6-'Metrics'!$F$6&lt;=0,'Metrics'!$O$6,'Metrics'!$N$6+('Metrics'!$B$6-'Metrics'!$F$6)/('Metrics'!$G$6-'Metrics'!$F$6)*('Metrics'!$O$6-'Metrics'!$N$6)),IF('Metrics'!$B$6&lt;='Metrics'!$H$6,IF('Metrics'!$H$6-'Metrics'!$G$6&lt;=0,'Metrics'!$P$6,'Metrics'!$O$6+('Metrics'!$B$6-'Metrics'!$G$6)/('Metrics'!$H$6-'Metrics'!$G$6)*('Metrics'!$P$6-'Metrics'!$O$6)),IF('Metrics'!$B$6&lt;='Metrics'!$I$6,IF('Metrics'!$I$6-'Metrics'!$H$6&lt;=0,'Metrics'!$Q$6,'Metrics'!$P$6+('Metrics'!$B$6-'Metrics'!$H$6)/('Metrics'!$I$6-'Metrics'!$H$6)*('Metrics'!$Q$6-'Metrics'!$P$6)),IF('Metrics'!$B$6&lt;='Metrics'!$J$6,IF('Metrics'!$J$6-'Metrics'!$I$6&lt;=0,'Metrics'!$R$6,'Metrics'!$Q$6+('Metrics'!$B$6-'Metrics'!$I$6)/('Metrics'!$J$6-'Metrics'!$I$6)*('Metrics'!$R$6-'Metrics'!$Q$6)),IF('Metrics'!$B$6&lt;='Metrics'!$K$6,IF('Metrics'!$K$6-'Metrics'!$J$6&lt;=0,'Metrics'!$S$6,'Metrics'!$R$6+('Metrics'!$B$6-'Metrics'!$J$6)/('Metrics'!$K$6-'Metrics'!$J$6)*('Metrics'!$S$6-'Metrics'!$R$6)),IF('Metrics'!$B$6&lt;='Metrics'!$L$6,IF('Metrics'!$L$6-'Metrics'!$K$6&lt;=0,'Metrics'!$T$6,'Metrics'!$S$6+('Metrics'!$B$6-'Metrics'!$K$6)/('Metrics'!$L$6-'Metrics'!$K$6)*('Metrics'!$T$6-'Metrics'!$S$6)),IF('Metrics'!$M$6-'Metrics'!$L$6&lt;=0,'Metrics'!$U$6,'Metrics'!$T$6+('Metrics'!$B$6-'Metrics'!$L$6)/('Metrics'!$M$6-'Metrics'!$L$6)*('Metrics'!$U$6-'Metrics'!$T$6)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>Wetland</t>
         </is>
       </c>
-      <c r="B7" s="72">
+      <c r="B7" s="73">
         <f>IF('DEEP Score'!$E$14="","",'DEEP Score'!$E$14)</f>
         <v/>
       </c>
-      <c r="C7" s="72">
+      <c r="C7" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D7" s="72">
+      <c r="D7" s="73">
         <f>"spring_pctwet2019ws|"&amp;'Metrics'!$C$7</f>
         <v/>
       </c>
-      <c r="E7" s="72">
+      <c r="E7" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$7,curve_key,0),MATCH("spring_pctwet2019ws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F7" s="72">
+      <c r="F7" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="G7" s="72">
+      <c r="G7" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="H7" s="72">
+      <c r="H7" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="T7" s="72">
+      <c r="T7" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="U7" s="72">
+      <c r="U7" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="V7" s="73">
+      <c r="V7" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$7),MAX(0,MIN(1,IF('Metrics'!$B$7&lt;='Metrics'!$F$7,'Metrics'!$N$7,IF('Metrics'!$B$7&gt;='Metrics'!$M$7,'Metrics'!$U$7,IF('Metrics'!$B$7&lt;='Metrics'!$G$7,IF('Metrics'!$G$7-'Metrics'!$F$7&lt;=0,'Metrics'!$O$7,'Metrics'!$N$7+('Metrics'!$B$7-'Metrics'!$F$7)/('Metrics'!$G$7-'Metrics'!$F$7)*('Metrics'!$O$7-'Metrics'!$N$7)),IF('Metrics'!$B$7&lt;='Metrics'!$H$7,IF('Metrics'!$H$7-'Metrics'!$G$7&lt;=0,'Metrics'!$P$7,'Metrics'!$O$7+('Metrics'!$B$7-'Metrics'!$G$7)/('Metrics'!$H$7-'Metrics'!$G$7)*('Metrics'!$P$7-'Metrics'!$O$7)),IF('Metrics'!$B$7&lt;='Metrics'!$I$7,IF('Metrics'!$I$7-'Metrics'!$H$7&lt;=0,'Metrics'!$Q$7,'Metrics'!$P$7+('Metrics'!$B$7-'Metrics'!$H$7)/('Metrics'!$I$7-'Metrics'!$H$7)*('Metrics'!$Q$7-'Metrics'!$P$7)),IF('Metrics'!$B$7&lt;='Metrics'!$J$7,IF('Metrics'!$J$7-'Metrics'!$I$7&lt;=0,'Metrics'!$R$7,'Metrics'!$Q$7+('Metrics'!$B$7-'Metrics'!$I$7)/('Metrics'!$J$7-'Metrics'!$I$7)*('Metrics'!$R$7-'Metrics'!$Q$7)),IF('Metrics'!$B$7&lt;='Metrics'!$K$7,IF('Metrics'!$K$7-'Metrics'!$J$7&lt;=0,'Metrics'!$S$7,'Metrics'!$R$7+('Metrics'!$B$7-'Metrics'!$J$7)/('Metrics'!$K$7-'Metrics'!$J$7)*('Metrics'!$S$7-'Metrics'!$R$7)),IF('Metrics'!$B$7&lt;='Metrics'!$L$7,IF('Metrics'!$L$7-'Metrics'!$K$7&lt;=0,'Metrics'!$T$7,'Metrics'!$S$7+('Metrics'!$B$7-'Metrics'!$K$7)/('Metrics'!$L$7-'Metrics'!$K$7)*('Metrics'!$T$7-'Metrics'!$S$7)),IF('Metrics'!$M$7-'Metrics'!$L$7&lt;=0,'Metrics'!$U$7,'Metrics'!$T$7+('Metrics'!$B$7-'Metrics'!$L$7)/('Metrics'!$M$7-'Metrics'!$L$7)*('Metrics'!$U$7-'Metrics'!$T$7)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>Road density</t>
         </is>
       </c>
-      <c r="B8" s="72">
+      <c r="B8" s="73">
         <f>IF('DEEP Score'!$E$15="","",'DEEP Score'!$E$15)</f>
         <v/>
       </c>
-      <c r="C8" s="72">
+      <c r="C8" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D8" s="72">
+      <c r="D8" s="73">
         <f>"spring_rddensws|"&amp;'Metrics'!$C$8</f>
         <v/>
       </c>
-      <c r="E8" s="72">
+      <c r="E8" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$8,curve_key,0),MATCH("spring_rddensws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F8" s="72">
+      <c r="F8" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="G8" s="72">
+      <c r="G8" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="H8" s="72">
+      <c r="H8" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="I8" s="72">
+      <c r="I8" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="J8" s="72">
+      <c r="J8" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="K8" s="72">
+      <c r="K8" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="L8" s="72">
+      <c r="L8" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="M8" s="72">
+      <c r="M8" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="O8" s="72">
+      <c r="O8" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="P8" s="72">
+      <c r="P8" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="Q8" s="72">
+      <c r="Q8" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="R8" s="72">
+      <c r="R8" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="S8" s="72">
+      <c r="S8" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="T8" s="72">
+      <c r="T8" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="U8" s="72">
+      <c r="U8" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="V8" s="73">
+      <c r="V8" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$8),MAX(0,MIN(1,IF('Metrics'!$B$8&lt;='Metrics'!$F$8,'Metrics'!$N$8,IF('Metrics'!$B$8&gt;='Metrics'!$M$8,'Metrics'!$U$8,IF('Metrics'!$B$8&lt;='Metrics'!$G$8,IF('Metrics'!$G$8-'Metrics'!$F$8&lt;=0,'Metrics'!$O$8,'Metrics'!$N$8+('Metrics'!$B$8-'Metrics'!$F$8)/('Metrics'!$G$8-'Metrics'!$F$8)*('Metrics'!$O$8-'Metrics'!$N$8)),IF('Metrics'!$B$8&lt;='Metrics'!$H$8,IF('Metrics'!$H$8-'Metrics'!$G$8&lt;=0,'Metrics'!$P$8,'Metrics'!$O$8+('Metrics'!$B$8-'Metrics'!$G$8)/('Metrics'!$H$8-'Metrics'!$G$8)*('Metrics'!$P$8-'Metrics'!$O$8)),IF('Metrics'!$B$8&lt;='Metrics'!$I$8,IF('Metrics'!$I$8-'Metrics'!$H$8&lt;=0,'Metrics'!$Q$8,'Metrics'!$P$8+('Metrics'!$B$8-'Metrics'!$H$8)/('Metrics'!$I$8-'Metrics'!$H$8)*('Metrics'!$Q$8-'Metrics'!$P$8)),IF('Metrics'!$B$8&lt;='Metrics'!$J$8,IF('Metrics'!$J$8-'Metrics'!$I$8&lt;=0,'Metrics'!$R$8,'Metrics'!$Q$8+('Metrics'!$B$8-'Metrics'!$I$8)/('Metrics'!$J$8-'Metrics'!$I$8)*('Metrics'!$R$8-'Metrics'!$Q$8)),IF('Metrics'!$B$8&lt;='Metrics'!$K$8,IF('Metrics'!$K$8-'Metrics'!$J$8&lt;=0,'Metrics'!$S$8,'Metrics'!$R$8+('Metrics'!$B$8-'Metrics'!$J$8)/('Metrics'!$K$8-'Metrics'!$J$8)*('Metrics'!$S$8-'Metrics'!$R$8)),IF('Metrics'!$B$8&lt;='Metrics'!$L$8,IF('Metrics'!$L$8-'Metrics'!$K$8&lt;=0,'Metrics'!$T$8,'Metrics'!$S$8+('Metrics'!$B$8-'Metrics'!$K$8)/('Metrics'!$L$8-'Metrics'!$K$8)*('Metrics'!$T$8-'Metrics'!$S$8)),IF('Metrics'!$M$8-'Metrics'!$L$8&lt;=0,'Metrics'!$U$8,'Metrics'!$T$8+('Metrics'!$B$8-'Metrics'!$L$8)/('Metrics'!$M$8-'Metrics'!$L$8)*('Metrics'!$U$8-'Metrics'!$T$8)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>Base flow index</t>
         </is>
       </c>
-      <c r="B9" s="72">
+      <c r="B9" s="73">
         <f>IF('DEEP Score'!$E$16="","",'DEEP Score'!$E$16)</f>
         <v/>
       </c>
-      <c r="C9" s="72">
+      <c r="C9" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D9" s="72">
+      <c r="D9" s="73">
         <f>"spring_bfiws|"&amp;'Metrics'!$C$9</f>
         <v/>
       </c>
-      <c r="E9" s="72">
+      <c r="E9" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$9,curve_key,0),MATCH("spring_bfiws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F9" s="72">
+      <c r="F9" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="G9" s="72">
+      <c r="G9" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="H9" s="72">
+      <c r="H9" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="I9" s="72">
+      <c r="I9" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="J9" s="72">
+      <c r="J9" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="K9" s="72">
+      <c r="K9" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="L9" s="72">
+      <c r="L9" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="M9" s="72">
+      <c r="M9" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="N9" s="72">
+      <c r="N9" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="O9" s="72">
+      <c r="O9" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="P9" s="72">
+      <c r="P9" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="Q9" s="72">
+      <c r="Q9" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="R9" s="72">
+      <c r="R9" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="S9" s="72">
+      <c r="S9" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="T9" s="72">
+      <c r="T9" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="U9" s="72">
+      <c r="U9" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="V9" s="73">
+      <c r="V9" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$9),MAX(0,MIN(1,IF('Metrics'!$B$9&lt;='Metrics'!$F$9,'Metrics'!$N$9,IF('Metrics'!$B$9&gt;='Metrics'!$M$9,'Metrics'!$U$9,IF('Metrics'!$B$9&lt;='Metrics'!$G$9,IF('Metrics'!$G$9-'Metrics'!$F$9&lt;=0,'Metrics'!$O$9,'Metrics'!$N$9+('Metrics'!$B$9-'Metrics'!$F$9)/('Metrics'!$G$9-'Metrics'!$F$9)*('Metrics'!$O$9-'Metrics'!$N$9)),IF('Metrics'!$B$9&lt;='Metrics'!$H$9,IF('Metrics'!$H$9-'Metrics'!$G$9&lt;=0,'Metrics'!$P$9,'Metrics'!$O$9+('Metrics'!$B$9-'Metrics'!$G$9)/('Metrics'!$H$9-'Metrics'!$G$9)*('Metrics'!$P$9-'Metrics'!$O$9)),IF('Metrics'!$B$9&lt;='Metrics'!$I$9,IF('Metrics'!$I$9-'Metrics'!$H$9&lt;=0,'Metrics'!$Q$9,'Metrics'!$P$9+('Metrics'!$B$9-'Metrics'!$H$9)/('Metrics'!$I$9-'Metrics'!$H$9)*('Metrics'!$Q$9-'Metrics'!$P$9)),IF('Metrics'!$B$9&lt;='Metrics'!$J$9,IF('Metrics'!$J$9-'Metrics'!$I$9&lt;=0,'Metrics'!$R$9,'Metrics'!$Q$9+('Metrics'!$B$9-'Metrics'!$I$9)/('Metrics'!$J$9-'Metrics'!$I$9)*('Metrics'!$R$9-'Metrics'!$Q$9)),IF('Metrics'!$B$9&lt;='Metrics'!$K$9,IF('Metrics'!$K$9-'Metrics'!$J$9&lt;=0,'Metrics'!$S$9,'Metrics'!$R$9+('Metrics'!$B$9-'Metrics'!$J$9)/('Metrics'!$K$9-'Metrics'!$J$9)*('Metrics'!$S$9-'Metrics'!$R$9)),IF('Metrics'!$B$9&lt;='Metrics'!$L$9,IF('Metrics'!$L$9-'Metrics'!$K$9&lt;=0,'Metrics'!$T$9,'Metrics'!$S$9+('Metrics'!$B$9-'Metrics'!$K$9)/('Metrics'!$L$9-'Metrics'!$K$9)*('Metrics'!$T$9-'Metrics'!$S$9)),IF('Metrics'!$M$9-'Metrics'!$L$9&lt;=0,'Metrics'!$U$9,'Metrics'!$T$9+('Metrics'!$B$9-'Metrics'!$L$9)/('Metrics'!$M$9-'Metrics'!$L$9)*('Metrics'!$U$9-'Metrics'!$T$9)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Degree of regulation</t>
         </is>
       </c>
-      <c r="B10" s="72">
+      <c r="B10" s="73">
         <f>IF('DEEP Score'!$E$17="","",'DEEP Score'!$E$17)</f>
         <v/>
       </c>
-      <c r="C10" s="72">
+      <c r="C10" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D10" s="72">
+      <c r="D10" s="73">
         <f>"spring_dorws|"&amp;'Metrics'!$C$10</f>
         <v/>
       </c>
-      <c r="E10" s="72">
+      <c r="E10" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$10,curve_key,0),MATCH("spring_dorws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F10" s="72">
+      <c r="F10" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="G10" s="72">
+      <c r="G10" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="H10" s="72">
+      <c r="H10" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="I10" s="72">
+      <c r="I10" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="J10" s="72">
+      <c r="J10" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="K10" s="72">
+      <c r="K10" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="L10" s="72">
+      <c r="L10" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="M10" s="72">
+      <c r="M10" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="N10" s="72">
+      <c r="N10" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="O10" s="72">
+      <c r="O10" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="P10" s="72">
+      <c r="P10" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="Q10" s="72">
+      <c r="Q10" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="R10" s="72">
+      <c r="R10" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="S10" s="72">
+      <c r="S10" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="T10" s="72">
+      <c r="T10" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="U10" s="72">
+      <c r="U10" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="V10" s="73">
+      <c r="V10" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$10),MAX(0,MIN(1,IF('Metrics'!$B$10&lt;='Metrics'!$F$10,'Metrics'!$N$10,IF('Metrics'!$B$10&gt;='Metrics'!$M$10,'Metrics'!$U$10,IF('Metrics'!$B$10&lt;='Metrics'!$G$10,IF('Metrics'!$G$10-'Metrics'!$F$10&lt;=0,'Metrics'!$O$10,'Metrics'!$N$10+('Metrics'!$B$10-'Metrics'!$F$10)/('Metrics'!$G$10-'Metrics'!$F$10)*('Metrics'!$O$10-'Metrics'!$N$10)),IF('Metrics'!$B$10&lt;='Metrics'!$H$10,IF('Metrics'!$H$10-'Metrics'!$G$10&lt;=0,'Metrics'!$P$10,'Metrics'!$O$10+('Metrics'!$B$10-'Metrics'!$G$10)/('Metrics'!$H$10-'Metrics'!$G$10)*('Metrics'!$P$10-'Metrics'!$O$10)),IF('Metrics'!$B$10&lt;='Metrics'!$I$10,IF('Metrics'!$I$10-'Metrics'!$H$10&lt;=0,'Metrics'!$Q$10,'Metrics'!$P$10+('Metrics'!$B$10-'Metrics'!$H$10)/('Metrics'!$I$10-'Metrics'!$H$10)*('Metrics'!$Q$10-'Metrics'!$P$10)),IF('Metrics'!$B$10&lt;='Metrics'!$J$10,IF('Metrics'!$J$10-'Metrics'!$I$10&lt;=0,'Metrics'!$R$10,'Metrics'!$Q$10+('Metrics'!$B$10-'Metrics'!$I$10)/('Metrics'!$J$10-'Metrics'!$I$10)*('Metrics'!$R$10-'Metrics'!$Q$10)),IF('Metrics'!$B$10&lt;='Metrics'!$K$10,IF('Metrics'!$K$10-'Metrics'!$J$10&lt;=0,'Metrics'!$S$10,'Metrics'!$R$10+('Metrics'!$B$10-'Metrics'!$J$10)/('Metrics'!$K$10-'Metrics'!$J$10)*('Metrics'!$S$10-'Metrics'!$R$10)),IF('Metrics'!$B$10&lt;='Metrics'!$L$10,IF('Metrics'!$L$10-'Metrics'!$K$10&lt;=0,'Metrics'!$T$10,'Metrics'!$S$10+('Metrics'!$B$10-'Metrics'!$K$10)/('Metrics'!$L$10-'Metrics'!$K$10)*('Metrics'!$T$10-'Metrics'!$S$10)),IF('Metrics'!$M$10-'Metrics'!$L$10&lt;=0,'Metrics'!$U$10,'Metrics'!$T$10+('Metrics'!$B$10-'Metrics'!$L$10)/('Metrics'!$M$10-'Metrics'!$L$10)*('Metrics'!$U$10-'Metrics'!$T$10)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>Bankfull width:depth ratio</t>
         </is>
       </c>
-      <c r="B11" s="72">
+      <c r="B11" s="73">
         <f>IF('DEEP Score'!$E$18="","",'DEEP Score'!$E$18)</f>
         <v/>
       </c>
-      <c r="C11" s="72">
+      <c r="C11" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D11" s="72">
+      <c r="D11" s="73">
         <f>"spring_phab_bfwd_rat|"&amp;'Metrics'!$C$11</f>
         <v/>
       </c>
-      <c r="E11" s="72">
+      <c r="E11" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$11,curve_key,0),MATCH("spring_phab_bfwd_rat|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F11" s="72">
+      <c r="F11" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="G11" s="72">
+      <c r="G11" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="H11" s="72">
+      <c r="H11" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="I11" s="72">
+      <c r="I11" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="J11" s="72">
+      <c r="J11" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="K11" s="72">
+      <c r="K11" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="L11" s="72">
+      <c r="L11" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="M11" s="72">
+      <c r="M11" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="N11" s="72">
+      <c r="N11" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="O11" s="72">
+      <c r="O11" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="P11" s="72">
+      <c r="P11" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="Q11" s="72">
+      <c r="Q11" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="R11" s="72">
+      <c r="R11" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="S11" s="72">
+      <c r="S11" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="T11" s="72">
+      <c r="T11" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="U11" s="72">
+      <c r="U11" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="V11" s="73">
+      <c r="V11" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$11),MAX(0,MIN(1,IF('Metrics'!$B$11&lt;='Metrics'!$F$11,'Metrics'!$N$11,IF('Metrics'!$B$11&gt;='Metrics'!$M$11,'Metrics'!$U$11,IF('Metrics'!$B$11&lt;='Metrics'!$G$11,IF('Metrics'!$G$11-'Metrics'!$F$11&lt;=0,'Metrics'!$O$11,'Metrics'!$N$11+('Metrics'!$B$11-'Metrics'!$F$11)/('Metrics'!$G$11-'Metrics'!$F$11)*('Metrics'!$O$11-'Metrics'!$N$11)),IF('Metrics'!$B$11&lt;='Metrics'!$H$11,IF('Metrics'!$H$11-'Metrics'!$G$11&lt;=0,'Metrics'!$P$11,'Metrics'!$O$11+('Metrics'!$B$11-'Metrics'!$G$11)/('Metrics'!$H$11-'Metrics'!$G$11)*('Metrics'!$P$11-'Metrics'!$O$11)),IF('Metrics'!$B$11&lt;='Metrics'!$I$11,IF('Metrics'!$I$11-'Metrics'!$H$11&lt;=0,'Metrics'!$Q$11,'Metrics'!$P$11+('Metrics'!$B$11-'Metrics'!$H$11)/('Metrics'!$I$11-'Metrics'!$H$11)*('Metrics'!$Q$11-'Metrics'!$P$11)),IF('Metrics'!$B$11&lt;='Metrics'!$J$11,IF('Metrics'!$J$11-'Metrics'!$I$11&lt;=0,'Metrics'!$R$11,'Metrics'!$Q$11+('Metrics'!$B$11-'Metrics'!$I$11)/('Metrics'!$J$11-'Metrics'!$I$11)*('Metrics'!$R$11-'Metrics'!$Q$11)),IF('Metrics'!$B$11&lt;='Metrics'!$K$11,IF('Metrics'!$K$11-'Metrics'!$J$11&lt;=0,'Metrics'!$S$11,'Metrics'!$R$11+('Metrics'!$B$11-'Metrics'!$J$11)/('Metrics'!$K$11-'Metrics'!$J$11)*('Metrics'!$S$11-'Metrics'!$R$11)),IF('Metrics'!$B$11&lt;='Metrics'!$L$11,IF('Metrics'!$L$11-'Metrics'!$K$11&lt;=0,'Metrics'!$T$11,'Metrics'!$S$11+('Metrics'!$B$11-'Metrics'!$K$11)/('Metrics'!$L$11-'Metrics'!$K$11)*('Metrics'!$T$11-'Metrics'!$S$11)),IF('Metrics'!$M$11-'Metrics'!$L$11&lt;=0,'Metrics'!$U$11,'Metrics'!$T$11+('Metrics'!$B$11-'Metrics'!$L$11)/('Metrics'!$M$11-'Metrics'!$L$11)*('Metrics'!$U$11-'Metrics'!$T$11)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Residual pool depth</t>
         </is>
       </c>
-      <c r="B12" s="72">
+      <c r="B12" s="73">
         <f>IF('DEEP Score'!$E$19="","",'DEEP Score'!$E$19)</f>
         <v/>
       </c>
-      <c r="C12" s="72">
+      <c r="C12" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D12" s="72">
+      <c r="D12" s="73">
         <f>"spring_phab_rp100_cm|"&amp;'Metrics'!$C$12</f>
         <v/>
       </c>
-      <c r="E12" s="72">
+      <c r="E12" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$12,curve_key,0),MATCH("spring_phab_rp100_cm|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F12" s="72">
+      <c r="F12" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="G12" s="72">
+      <c r="G12" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="H12" s="72">
+      <c r="H12" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="I12" s="72">
+      <c r="I12" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="J12" s="72">
+      <c r="J12" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="K12" s="72">
+      <c r="K12" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="L12" s="72">
+      <c r="L12" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="M12" s="72">
+      <c r="M12" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="N12" s="72">
+      <c r="N12" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="O12" s="72">
+      <c r="O12" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="P12" s="72">
+      <c r="P12" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="Q12" s="72">
+      <c r="Q12" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="R12" s="72">
+      <c r="R12" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="S12" s="72">
+      <c r="S12" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="T12" s="72">
+      <c r="T12" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="U12" s="72">
+      <c r="U12" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="V12" s="73">
+      <c r="V12" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$12),MAX(0,MIN(1,IF('Metrics'!$B$12&lt;='Metrics'!$F$12,'Metrics'!$N$12,IF('Metrics'!$B$12&gt;='Metrics'!$M$12,'Metrics'!$U$12,IF('Metrics'!$B$12&lt;='Metrics'!$G$12,IF('Metrics'!$G$12-'Metrics'!$F$12&lt;=0,'Metrics'!$O$12,'Metrics'!$N$12+('Metrics'!$B$12-'Metrics'!$F$12)/('Metrics'!$G$12-'Metrics'!$F$12)*('Metrics'!$O$12-'Metrics'!$N$12)),IF('Metrics'!$B$12&lt;='Metrics'!$H$12,IF('Metrics'!$H$12-'Metrics'!$G$12&lt;=0,'Metrics'!$P$12,'Metrics'!$O$12+('Metrics'!$B$12-'Metrics'!$G$12)/('Metrics'!$H$12-'Metrics'!$G$12)*('Metrics'!$P$12-'Metrics'!$O$12)),IF('Metrics'!$B$12&lt;='Metrics'!$I$12,IF('Metrics'!$I$12-'Metrics'!$H$12&lt;=0,'Metrics'!$Q$12,'Metrics'!$P$12+('Metrics'!$B$12-'Metrics'!$H$12)/('Metrics'!$I$12-'Metrics'!$H$12)*('Metrics'!$Q$12-'Metrics'!$P$12)),IF('Metrics'!$B$12&lt;='Metrics'!$J$12,IF('Metrics'!$J$12-'Metrics'!$I$12&lt;=0,'Metrics'!$R$12,'Metrics'!$Q$12+('Metrics'!$B$12-'Metrics'!$I$12)/('Metrics'!$J$12-'Metrics'!$I$12)*('Metrics'!$R$12-'Metrics'!$Q$12)),IF('Metrics'!$B$12&lt;='Metrics'!$K$12,IF('Metrics'!$K$12-'Metrics'!$J$12&lt;=0,'Metrics'!$S$12,'Metrics'!$R$12+('Metrics'!$B$12-'Metrics'!$J$12)/('Metrics'!$K$12-'Metrics'!$J$12)*('Metrics'!$S$12-'Metrics'!$R$12)),IF('Metrics'!$B$12&lt;='Metrics'!$L$12,IF('Metrics'!$L$12-'Metrics'!$K$12&lt;=0,'Metrics'!$T$12,'Metrics'!$S$12+('Metrics'!$B$12-'Metrics'!$K$12)/('Metrics'!$L$12-'Metrics'!$K$12)*('Metrics'!$T$12-'Metrics'!$S$12)),IF('Metrics'!$M$12-'Metrics'!$L$12&lt;=0,'Metrics'!$U$12,'Metrics'!$T$12+('Metrics'!$B$12-'Metrics'!$L$12)/('Metrics'!$M$12-'Metrics'!$L$12)*('Metrics'!$U$12-'Metrics'!$T$12)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>Bankfull height above channel</t>
         </is>
       </c>
-      <c r="B13" s="72">
+      <c r="B13" s="73">
         <f>IF('DEEP Score'!$E$23="","",'DEEP Score'!$E$23)</f>
         <v/>
       </c>
-      <c r="C13" s="72">
+      <c r="C13" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D13" s="72">
+      <c r="D13" s="73">
         <f>"spring_phab_xbkf_h|"&amp;'Metrics'!$C$13</f>
         <v/>
       </c>
-      <c r="E13" s="72">
+      <c r="E13" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$13,curve_key,0),MATCH("spring_phab_xbkf_h|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F13" s="72">
+      <c r="F13" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="G13" s="72">
+      <c r="G13" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="H13" s="72">
+      <c r="H13" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="I13" s="72">
+      <c r="I13" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="J13" s="72">
+      <c r="J13" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="K13" s="72">
+      <c r="K13" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="L13" s="72">
+      <c r="L13" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="M13" s="72">
+      <c r="M13" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="N13" s="72">
+      <c r="N13" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="O13" s="72">
+      <c r="O13" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="P13" s="72">
+      <c r="P13" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="Q13" s="72">
+      <c r="Q13" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="R13" s="72">
+      <c r="R13" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="S13" s="72">
+      <c r="S13" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="T13" s="72">
+      <c r="T13" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="U13" s="72">
+      <c r="U13" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="V13" s="73">
+      <c r="V13" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$13),MAX(0,MIN(1,IF('Metrics'!$B$13&lt;='Metrics'!$F$13,'Metrics'!$N$13,IF('Metrics'!$B$13&gt;='Metrics'!$M$13,'Metrics'!$U$13,IF('Metrics'!$B$13&lt;='Metrics'!$G$13,IF('Metrics'!$G$13-'Metrics'!$F$13&lt;=0,'Metrics'!$O$13,'Metrics'!$N$13+('Metrics'!$B$13-'Metrics'!$F$13)/('Metrics'!$G$13-'Metrics'!$F$13)*('Metrics'!$O$13-'Metrics'!$N$13)),IF('Metrics'!$B$13&lt;='Metrics'!$H$13,IF('Metrics'!$H$13-'Metrics'!$G$13&lt;=0,'Metrics'!$P$13,'Metrics'!$O$13+('Metrics'!$B$13-'Metrics'!$G$13)/('Metrics'!$H$13-'Metrics'!$G$13)*('Metrics'!$P$13-'Metrics'!$O$13)),IF('Metrics'!$B$13&lt;='Metrics'!$I$13,IF('Metrics'!$I$13-'Metrics'!$H$13&lt;=0,'Metrics'!$Q$13,'Metrics'!$P$13+('Metrics'!$B$13-'Metrics'!$H$13)/('Metrics'!$I$13-'Metrics'!$H$13)*('Metrics'!$Q$13-'Metrics'!$P$13)),IF('Metrics'!$B$13&lt;='Metrics'!$J$13,IF('Metrics'!$J$13-'Metrics'!$I$13&lt;=0,'Metrics'!$R$13,'Metrics'!$Q$13+('Metrics'!$B$13-'Metrics'!$I$13)/('Metrics'!$J$13-'Metrics'!$I$13)*('Metrics'!$R$13-'Metrics'!$Q$13)),IF('Metrics'!$B$13&lt;='Metrics'!$K$13,IF('Metrics'!$K$13-'Metrics'!$J$13&lt;=0,'Metrics'!$S$13,'Metrics'!$R$13+('Metrics'!$B$13-'Metrics'!$J$13)/('Metrics'!$K$13-'Metrics'!$J$13)*('Metrics'!$S$13-'Metrics'!$R$13)),IF('Metrics'!$B$13&lt;='Metrics'!$L$13,IF('Metrics'!$L$13-'Metrics'!$K$13&lt;=0,'Metrics'!$T$13,'Metrics'!$S$13+('Metrics'!$B$13-'Metrics'!$K$13)/('Metrics'!$L$13-'Metrics'!$K$13)*('Metrics'!$T$13-'Metrics'!$S$13)),IF('Metrics'!$M$13-'Metrics'!$L$13&lt;=0,'Metrics'!$U$13,'Metrics'!$T$13+('Metrics'!$B$13-'Metrics'!$L$13)/('Metrics'!$M$13-'Metrics'!$L$13)*('Metrics'!$U$13-'Metrics'!$T$13)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>Sand + fines</t>
         </is>
       </c>
-      <c r="B14" s="72">
+      <c r="B14" s="73">
         <f>IF('DEEP Score'!$E$24="","",'DEEP Score'!$E$24)</f>
         <v/>
       </c>
-      <c r="C14" s="72">
+      <c r="C14" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D14" s="72">
+      <c r="D14" s="73">
         <f>"spring_phab_pct_safn|"&amp;'Metrics'!$C$14</f>
         <v/>
       </c>
-      <c r="E14" s="72">
+      <c r="E14" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$14,curve_key,0),MATCH("spring_phab_pct_safn|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F14" s="72">
+      <c r="F14" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="G14" s="72">
+      <c r="G14" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="H14" s="72">
+      <c r="H14" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="I14" s="72">
+      <c r="I14" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="J14" s="72">
+      <c r="J14" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="K14" s="72">
+      <c r="K14" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="L14" s="72">
+      <c r="L14" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="M14" s="72">
+      <c r="M14" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="N14" s="72">
+      <c r="N14" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="O14" s="72">
+      <c r="O14" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="P14" s="72">
+      <c r="P14" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="Q14" s="72">
+      <c r="Q14" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="R14" s="72">
+      <c r="R14" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="S14" s="72">
+      <c r="S14" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="T14" s="72">
+      <c r="T14" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="U14" s="72">
+      <c r="U14" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="V14" s="73">
+      <c r="V14" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$14),MAX(0,MIN(1,IF('Metrics'!$B$14&lt;='Metrics'!$F$14,'Metrics'!$N$14,IF('Metrics'!$B$14&gt;='Metrics'!$M$14,'Metrics'!$U$14,IF('Metrics'!$B$14&lt;='Metrics'!$G$14,IF('Metrics'!$G$14-'Metrics'!$F$14&lt;=0,'Metrics'!$O$14,'Metrics'!$N$14+('Metrics'!$B$14-'Metrics'!$F$14)/('Metrics'!$G$14-'Metrics'!$F$14)*('Metrics'!$O$14-'Metrics'!$N$14)),IF('Metrics'!$B$14&lt;='Metrics'!$H$14,IF('Metrics'!$H$14-'Metrics'!$G$14&lt;=0,'Metrics'!$P$14,'Metrics'!$O$14+('Metrics'!$B$14-'Metrics'!$G$14)/('Metrics'!$H$14-'Metrics'!$G$14)*('Metrics'!$P$14-'Metrics'!$O$14)),IF('Metrics'!$B$14&lt;='Metrics'!$I$14,IF('Metrics'!$I$14-'Metrics'!$H$14&lt;=0,'Metrics'!$Q$14,'Metrics'!$P$14+('Metrics'!$B$14-'Metrics'!$H$14)/('Metrics'!$I$14-'Metrics'!$H$14)*('Metrics'!$Q$14-'Metrics'!$P$14)),IF('Metrics'!$B$14&lt;='Metrics'!$J$14,IF('Metrics'!$J$14-'Metrics'!$I$14&lt;=0,'Metrics'!$R$14,'Metrics'!$Q$14+('Metrics'!$B$14-'Metrics'!$I$14)/('Metrics'!$J$14-'Metrics'!$I$14)*('Metrics'!$R$14-'Metrics'!$Q$14)),IF('Metrics'!$B$14&lt;='Metrics'!$K$14,IF('Metrics'!$K$14-'Metrics'!$J$14&lt;=0,'Metrics'!$S$14,'Metrics'!$R$14+('Metrics'!$B$14-'Metrics'!$J$14)/('Metrics'!$K$14-'Metrics'!$J$14)*('Metrics'!$S$14-'Metrics'!$R$14)),IF('Metrics'!$B$14&lt;='Metrics'!$L$14,IF('Metrics'!$L$14-'Metrics'!$K$14&lt;=0,'Metrics'!$T$14,'Metrics'!$S$14+('Metrics'!$B$14-'Metrics'!$K$14)/('Metrics'!$L$14-'Metrics'!$K$14)*('Metrics'!$T$14-'Metrics'!$S$14)),IF('Metrics'!$M$14-'Metrics'!$L$14&lt;=0,'Metrics'!$U$14,'Metrics'!$T$14+('Metrics'!$B$14-'Metrics'!$L$14)/('Metrics'!$M$14-'Metrics'!$L$14)*('Metrics'!$U$14-'Metrics'!$T$14)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>Embeddedness</t>
         </is>
       </c>
-      <c r="B15" s="72">
+      <c r="B15" s="73">
         <f>IF('DEEP Score'!$E$25="","",'DEEP Score'!$E$25)</f>
         <v/>
       </c>
-      <c r="C15" s="72">
+      <c r="C15" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D15" s="72">
+      <c r="D15" s="73">
         <f>"spring_phab_xembed|"&amp;'Metrics'!$C$15</f>
         <v/>
       </c>
-      <c r="E15" s="72">
+      <c r="E15" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$15,curve_key,0),MATCH("spring_phab_xembed|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F15" s="72">
+      <c r="F15" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="G15" s="72">
+      <c r="G15" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="H15" s="72">
+      <c r="H15" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="I15" s="72">
+      <c r="I15" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="J15" s="72">
+      <c r="J15" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="K15" s="72">
+      <c r="K15" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="L15" s="72">
+      <c r="L15" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="M15" s="72">
+      <c r="M15" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="N15" s="72">
+      <c r="N15" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="O15" s="72">
+      <c r="O15" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="P15" s="72">
+      <c r="P15" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="Q15" s="72">
+      <c r="Q15" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="R15" s="72">
+      <c r="R15" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="S15" s="72">
+      <c r="S15" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="T15" s="72">
+      <c r="T15" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="U15" s="72">
+      <c r="U15" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="V15" s="73">
+      <c r="V15" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$15),MAX(0,MIN(1,IF('Metrics'!$B$15&lt;='Metrics'!$F$15,'Metrics'!$N$15,IF('Metrics'!$B$15&gt;='Metrics'!$M$15,'Metrics'!$U$15,IF('Metrics'!$B$15&lt;='Metrics'!$G$15,IF('Metrics'!$G$15-'Metrics'!$F$15&lt;=0,'Metrics'!$O$15,'Metrics'!$N$15+('Metrics'!$B$15-'Metrics'!$F$15)/('Metrics'!$G$15-'Metrics'!$F$15)*('Metrics'!$O$15-'Metrics'!$N$15)),IF('Metrics'!$B$15&lt;='Metrics'!$H$15,IF('Metrics'!$H$15-'Metrics'!$G$15&lt;=0,'Metrics'!$P$15,'Metrics'!$O$15+('Metrics'!$B$15-'Metrics'!$G$15)/('Metrics'!$H$15-'Metrics'!$G$15)*('Metrics'!$P$15-'Metrics'!$O$15)),IF('Metrics'!$B$15&lt;='Metrics'!$I$15,IF('Metrics'!$I$15-'Metrics'!$H$15&lt;=0,'Metrics'!$Q$15,'Metrics'!$P$15+('Metrics'!$B$15-'Metrics'!$H$15)/('Metrics'!$I$15-'Metrics'!$H$15)*('Metrics'!$Q$15-'Metrics'!$P$15)),IF('Metrics'!$B$15&lt;='Metrics'!$J$15,IF('Metrics'!$J$15-'Metrics'!$I$15&lt;=0,'Metrics'!$R$15,'Metrics'!$Q$15+('Metrics'!$B$15-'Metrics'!$I$15)/('Metrics'!$J$15-'Metrics'!$I$15)*('Metrics'!$R$15-'Metrics'!$Q$15)),IF('Metrics'!$B$15&lt;='Metrics'!$K$15,IF('Metrics'!$K$15-'Metrics'!$J$15&lt;=0,'Metrics'!$S$15,'Metrics'!$R$15+('Metrics'!$B$15-'Metrics'!$J$15)/('Metrics'!$K$15-'Metrics'!$J$15)*('Metrics'!$S$15-'Metrics'!$R$15)),IF('Metrics'!$B$15&lt;='Metrics'!$L$15,IF('Metrics'!$L$15-'Metrics'!$K$15&lt;=0,'Metrics'!$T$15,'Metrics'!$S$15+('Metrics'!$B$15-'Metrics'!$K$15)/('Metrics'!$L$15-'Metrics'!$K$15)*('Metrics'!$T$15-'Metrics'!$S$15)),IF('Metrics'!$M$15-'Metrics'!$L$15&lt;=0,'Metrics'!$U$15,'Metrics'!$T$15+('Metrics'!$B$15-'Metrics'!$L$15)/('Metrics'!$M$15-'Metrics'!$L$15)*('Metrics'!$U$15-'Metrics'!$T$15)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Sinuosity</t>
         </is>
       </c>
-      <c r="B16" s="72">
+      <c r="B16" s="73">
         <f>IF('DEEP Score'!$E$28="","",'DEEP Score'!$E$28)</f>
         <v/>
       </c>
-      <c r="C16" s="72">
+      <c r="C16" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D16" s="72">
+      <c r="D16" s="73">
         <f>"spring_phab_sinu|"&amp;'Metrics'!$C$16</f>
         <v/>
       </c>
-      <c r="E16" s="72">
+      <c r="E16" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$16,curve_key,0),MATCH("spring_phab_sinu|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F16" s="72">
+      <c r="F16" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="G16" s="72">
+      <c r="G16" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="H16" s="72">
+      <c r="H16" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="I16" s="72">
+      <c r="I16" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="J16" s="72">
+      <c r="J16" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="K16" s="72">
+      <c r="K16" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="L16" s="72">
+      <c r="L16" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="M16" s="72">
+      <c r="M16" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="N16" s="72">
+      <c r="N16" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="O16" s="72">
+      <c r="O16" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="P16" s="72">
+      <c r="P16" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="Q16" s="72">
+      <c r="Q16" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="R16" s="72">
+      <c r="R16" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="S16" s="72">
+      <c r="S16" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="T16" s="72">
+      <c r="T16" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="U16" s="72">
+      <c r="U16" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="V16" s="73">
+      <c r="V16" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$16),MAX(0,MIN(1,IF('Metrics'!$B$16&lt;='Metrics'!$F$16,'Metrics'!$N$16,IF('Metrics'!$B$16&gt;='Metrics'!$M$16,'Metrics'!$U$16,IF('Metrics'!$B$16&lt;='Metrics'!$G$16,IF('Metrics'!$G$16-'Metrics'!$F$16&lt;=0,'Metrics'!$O$16,'Metrics'!$N$16+('Metrics'!$B$16-'Metrics'!$F$16)/('Metrics'!$G$16-'Metrics'!$F$16)*('Metrics'!$O$16-'Metrics'!$N$16)),IF('Metrics'!$B$16&lt;='Metrics'!$H$16,IF('Metrics'!$H$16-'Metrics'!$G$16&lt;=0,'Metrics'!$P$16,'Metrics'!$O$16+('Metrics'!$B$16-'Metrics'!$G$16)/('Metrics'!$H$16-'Metrics'!$G$16)*('Metrics'!$P$16-'Metrics'!$O$16)),IF('Metrics'!$B$16&lt;='Metrics'!$I$16,IF('Metrics'!$I$16-'Metrics'!$H$16&lt;=0,'Metrics'!$Q$16,'Metrics'!$P$16+('Metrics'!$B$16-'Metrics'!$H$16)/('Metrics'!$I$16-'Metrics'!$H$16)*('Metrics'!$Q$16-'Metrics'!$P$16)),IF('Metrics'!$B$16&lt;='Metrics'!$J$16,IF('Metrics'!$J$16-'Metrics'!$I$16&lt;=0,'Metrics'!$R$16,'Metrics'!$Q$16+('Metrics'!$B$16-'Metrics'!$I$16)/('Metrics'!$J$16-'Metrics'!$I$16)*('Metrics'!$R$16-'Metrics'!$Q$16)),IF('Metrics'!$B$16&lt;='Metrics'!$K$16,IF('Metrics'!$K$16-'Metrics'!$J$16&lt;=0,'Metrics'!$S$16,'Metrics'!$R$16+('Metrics'!$B$16-'Metrics'!$J$16)/('Metrics'!$K$16-'Metrics'!$J$16)*('Metrics'!$S$16-'Metrics'!$R$16)),IF('Metrics'!$B$16&lt;='Metrics'!$L$16,IF('Metrics'!$L$16-'Metrics'!$K$16&lt;=0,'Metrics'!$T$16,'Metrics'!$S$16+('Metrics'!$B$16-'Metrics'!$K$16)/('Metrics'!$L$16-'Metrics'!$K$16)*('Metrics'!$T$16-'Metrics'!$S$16)),IF('Metrics'!$M$16-'Metrics'!$L$16&lt;=0,'Metrics'!$U$16,'Metrics'!$T$16+('Metrics'!$B$16-'Metrics'!$L$16)/('Metrics'!$M$16-'Metrics'!$L$16)*('Metrics'!$U$16-'Metrics'!$T$16)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Bank angle</t>
         </is>
       </c>
-      <c r="B17" s="72">
+      <c r="B17" s="73">
         <f>IF('DEEP Score'!$E$29="","",'DEEP Score'!$E$29)</f>
         <v/>
       </c>
-      <c r="C17" s="72">
+      <c r="C17" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D17" s="72">
+      <c r="D17" s="73">
         <f>"spring_phab_xbka|"&amp;'Metrics'!$C$17</f>
         <v/>
       </c>
-      <c r="E17" s="72">
+      <c r="E17" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$17,curve_key,0),MATCH("spring_phab_xbka|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F17" s="72">
+      <c r="F17" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="G17" s="72">
+      <c r="G17" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="H17" s="72">
+      <c r="H17" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="I17" s="72">
+      <c r="I17" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="J17" s="72">
+      <c r="J17" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="K17" s="72">
+      <c r="K17" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="L17" s="72">
+      <c r="L17" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="M17" s="72">
+      <c r="M17" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="N17" s="72">
+      <c r="N17" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="O17" s="72">
+      <c r="O17" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="P17" s="72">
+      <c r="P17" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="Q17" s="72">
+      <c r="Q17" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="R17" s="72">
+      <c r="R17" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="S17" s="72">
+      <c r="S17" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="T17" s="72">
+      <c r="T17" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="U17" s="72">
+      <c r="U17" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="V17" s="73">
+      <c r="V17" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$17),MAX(0,MIN(1,IF('Metrics'!$B$17&lt;='Metrics'!$F$17,'Metrics'!$N$17,IF('Metrics'!$B$17&gt;='Metrics'!$M$17,'Metrics'!$U$17,IF('Metrics'!$B$17&lt;='Metrics'!$G$17,IF('Metrics'!$G$17-'Metrics'!$F$17&lt;=0,'Metrics'!$O$17,'Metrics'!$N$17+('Metrics'!$B$17-'Metrics'!$F$17)/('Metrics'!$G$17-'Metrics'!$F$17)*('Metrics'!$O$17-'Metrics'!$N$17)),IF('Metrics'!$B$17&lt;='Metrics'!$H$17,IF('Metrics'!$H$17-'Metrics'!$G$17&lt;=0,'Metrics'!$P$17,'Metrics'!$O$17+('Metrics'!$B$17-'Metrics'!$G$17)/('Metrics'!$H$17-'Metrics'!$G$17)*('Metrics'!$P$17-'Metrics'!$O$17)),IF('Metrics'!$B$17&lt;='Metrics'!$I$17,IF('Metrics'!$I$17-'Metrics'!$H$17&lt;=0,'Metrics'!$Q$17,'Metrics'!$P$17+('Metrics'!$B$17-'Metrics'!$H$17)/('Metrics'!$I$17-'Metrics'!$H$17)*('Metrics'!$Q$17-'Metrics'!$P$17)),IF('Metrics'!$B$17&lt;='Metrics'!$J$17,IF('Metrics'!$J$17-'Metrics'!$I$17&lt;=0,'Metrics'!$R$17,'Metrics'!$Q$17+('Metrics'!$B$17-'Metrics'!$I$17)/('Metrics'!$J$17-'Metrics'!$I$17)*('Metrics'!$R$17-'Metrics'!$Q$17)),IF('Metrics'!$B$17&lt;='Metrics'!$K$17,IF('Metrics'!$K$17-'Metrics'!$J$17&lt;=0,'Metrics'!$S$17,'Metrics'!$R$17+('Metrics'!$B$17-'Metrics'!$J$17)/('Metrics'!$K$17-'Metrics'!$J$17)*('Metrics'!$S$17-'Metrics'!$R$17)),IF('Metrics'!$B$17&lt;='Metrics'!$L$17,IF('Metrics'!$L$17-'Metrics'!$K$17&lt;=0,'Metrics'!$T$17,'Metrics'!$S$17+('Metrics'!$B$17-'Metrics'!$K$17)/('Metrics'!$L$17-'Metrics'!$K$17)*('Metrics'!$T$17-'Metrics'!$S$17)),IF('Metrics'!$M$17-'Metrics'!$L$17&lt;=0,'Metrics'!$U$17,'Metrics'!$T$17+('Metrics'!$B$17-'Metrics'!$L$17)/('Metrics'!$M$17-'Metrics'!$L$17)*('Metrics'!$U$17-'Metrics'!$T$17)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>Relative bed stability</t>
         </is>
       </c>
-      <c r="B18" s="72">
+      <c r="B18" s="73">
         <f>IF('DEEP Score'!$E$30="","",'DEEP Score'!$E$30)</f>
         <v/>
       </c>
-      <c r="C18" s="72">
+      <c r="C18" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D18" s="72">
+      <c r="D18" s="73">
         <f>"spring_phab_lrbs_use|"&amp;'Metrics'!$C$18</f>
         <v/>
       </c>
-      <c r="E18" s="72">
+      <c r="E18" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$18,curve_key,0),MATCH("spring_phab_lrbs_use|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F18" s="72">
+      <c r="F18" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="G18" s="72">
+      <c r="G18" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="H18" s="72">
+      <c r="H18" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="I18" s="72">
+      <c r="I18" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="J18" s="72">
+      <c r="J18" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="K18" s="72">
+      <c r="K18" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="L18" s="72">
+      <c r="L18" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="M18" s="72">
+      <c r="M18" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="N18" s="72">
+      <c r="N18" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="O18" s="72">
+      <c r="O18" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="P18" s="72">
+      <c r="P18" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="Q18" s="72">
+      <c r="Q18" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="R18" s="72">
+      <c r="R18" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="S18" s="72">
+      <c r="S18" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="T18" s="72">
+      <c r="T18" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="U18" s="72">
+      <c r="U18" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="V18" s="73">
+      <c r="V18" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$18),MAX(0,MIN(1,IF('Metrics'!$B$18&lt;='Metrics'!$F$18,'Metrics'!$N$18,IF('Metrics'!$B$18&gt;='Metrics'!$M$18,'Metrics'!$U$18,IF('Metrics'!$B$18&lt;='Metrics'!$G$18,IF('Metrics'!$G$18-'Metrics'!$F$18&lt;=0,'Metrics'!$O$18,'Metrics'!$N$18+('Metrics'!$B$18-'Metrics'!$F$18)/('Metrics'!$G$18-'Metrics'!$F$18)*('Metrics'!$O$18-'Metrics'!$N$18)),IF('Metrics'!$B$18&lt;='Metrics'!$H$18,IF('Metrics'!$H$18-'Metrics'!$G$18&lt;=0,'Metrics'!$P$18,'Metrics'!$O$18+('Metrics'!$B$18-'Metrics'!$G$18)/('Metrics'!$H$18-'Metrics'!$G$18)*('Metrics'!$P$18-'Metrics'!$O$18)),IF('Metrics'!$B$18&lt;='Metrics'!$I$18,IF('Metrics'!$I$18-'Metrics'!$H$18&lt;=0,'Metrics'!$Q$18,'Metrics'!$P$18+('Metrics'!$B$18-'Metrics'!$H$18)/('Metrics'!$I$18-'Metrics'!$H$18)*('Metrics'!$Q$18-'Metrics'!$P$18)),IF('Metrics'!$B$18&lt;='Metrics'!$J$18,IF('Metrics'!$J$18-'Metrics'!$I$18&lt;=0,'Metrics'!$R$18,'Metrics'!$Q$18+('Metrics'!$B$18-'Metrics'!$I$18)/('Metrics'!$J$18-'Metrics'!$I$18)*('Metrics'!$R$18-'Metrics'!$Q$18)),IF('Metrics'!$B$18&lt;='Metrics'!$K$18,IF('Metrics'!$K$18-'Metrics'!$J$18&lt;=0,'Metrics'!$S$18,'Metrics'!$R$18+('Metrics'!$B$18-'Metrics'!$J$18)/('Metrics'!$K$18-'Metrics'!$J$18)*('Metrics'!$S$18-'Metrics'!$R$18)),IF('Metrics'!$B$18&lt;='Metrics'!$L$18,IF('Metrics'!$L$18-'Metrics'!$K$18&lt;=0,'Metrics'!$T$18,'Metrics'!$S$18+('Metrics'!$B$18-'Metrics'!$K$18)/('Metrics'!$L$18-'Metrics'!$K$18)*('Metrics'!$T$18-'Metrics'!$S$18)),IF('Metrics'!$M$18-'Metrics'!$L$18&lt;=0,'Metrics'!$U$18,'Metrics'!$T$18+('Metrics'!$B$18-'Metrics'!$L$18)/('Metrics'!$M$18-'Metrics'!$L$18)*('Metrics'!$U$18-'Metrics'!$T$18)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>Substrate size</t>
         </is>
       </c>
-      <c r="B19" s="72">
+      <c r="B19" s="73">
         <f>IF('DEEP Score'!$E$32="","",'DEEP Score'!$E$32)</f>
         <v/>
       </c>
-      <c r="C19" s="72">
+      <c r="C19" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D19" s="72">
+      <c r="D19" s="73">
         <f>"spring_phab_lsub_dmm|"&amp;'Metrics'!$C$19</f>
         <v/>
       </c>
-      <c r="E19" s="72">
+      <c r="E19" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$19,curve_key,0),MATCH("spring_phab_lsub_dmm|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F19" s="72">
+      <c r="F19" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="G19" s="72">
+      <c r="G19" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="H19" s="72">
+      <c r="H19" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="I19" s="72">
+      <c r="I19" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="J19" s="72">
+      <c r="J19" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="K19" s="72">
+      <c r="K19" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="L19" s="72">
+      <c r="L19" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="M19" s="72">
+      <c r="M19" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="N19" s="72">
+      <c r="N19" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="O19" s="72">
+      <c r="O19" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="P19" s="72">
+      <c r="P19" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="Q19" s="72">
+      <c r="Q19" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="R19" s="72">
+      <c r="R19" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="S19" s="72">
+      <c r="S19" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="T19" s="72">
+      <c r="T19" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="U19" s="72">
+      <c r="U19" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="V19" s="73">
+      <c r="V19" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$19),MAX(0,MIN(1,IF('Metrics'!$B$19&lt;='Metrics'!$F$19,'Metrics'!$N$19,IF('Metrics'!$B$19&gt;='Metrics'!$M$19,'Metrics'!$U$19,IF('Metrics'!$B$19&lt;='Metrics'!$G$19,IF('Metrics'!$G$19-'Metrics'!$F$19&lt;=0,'Metrics'!$O$19,'Metrics'!$N$19+('Metrics'!$B$19-'Metrics'!$F$19)/('Metrics'!$G$19-'Metrics'!$F$19)*('Metrics'!$O$19-'Metrics'!$N$19)),IF('Metrics'!$B$19&lt;='Metrics'!$H$19,IF('Metrics'!$H$19-'Metrics'!$G$19&lt;=0,'Metrics'!$P$19,'Metrics'!$O$19+('Metrics'!$B$19-'Metrics'!$G$19)/('Metrics'!$H$19-'Metrics'!$G$19)*('Metrics'!$P$19-'Metrics'!$O$19)),IF('Metrics'!$B$19&lt;='Metrics'!$I$19,IF('Metrics'!$I$19-'Metrics'!$H$19&lt;=0,'Metrics'!$Q$19,'Metrics'!$P$19+('Metrics'!$B$19-'Metrics'!$H$19)/('Metrics'!$I$19-'Metrics'!$H$19)*('Metrics'!$Q$19-'Metrics'!$P$19)),IF('Metrics'!$B$19&lt;='Metrics'!$J$19,IF('Metrics'!$J$19-'Metrics'!$I$19&lt;=0,'Metrics'!$R$19,'Metrics'!$Q$19+('Metrics'!$B$19-'Metrics'!$I$19)/('Metrics'!$J$19-'Metrics'!$I$19)*('Metrics'!$R$19-'Metrics'!$Q$19)),IF('Metrics'!$B$19&lt;='Metrics'!$K$19,IF('Metrics'!$K$19-'Metrics'!$J$19&lt;=0,'Metrics'!$S$19,'Metrics'!$R$19+('Metrics'!$B$19-'Metrics'!$J$19)/('Metrics'!$K$19-'Metrics'!$J$19)*('Metrics'!$S$19-'Metrics'!$R$19)),IF('Metrics'!$B$19&lt;='Metrics'!$L$19,IF('Metrics'!$L$19-'Metrics'!$K$19&lt;=0,'Metrics'!$T$19,'Metrics'!$S$19+('Metrics'!$B$19-'Metrics'!$K$19)/('Metrics'!$L$19-'Metrics'!$K$19)*('Metrics'!$T$19-'Metrics'!$S$19)),IF('Metrics'!$M$19-'Metrics'!$L$19&lt;=0,'Metrics'!$U$19,'Metrics'!$T$19+('Metrics'!$B$19-'Metrics'!$L$19)/('Metrics'!$M$19-'Metrics'!$L$19)*('Metrics'!$U$19-'Metrics'!$T$19)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>Large wood volume</t>
         </is>
       </c>
-      <c r="B20" s="72">
+      <c r="B20" s="73">
         <f>IF('DEEP Score'!$E$33="","",'DEEP Score'!$E$33)</f>
         <v/>
       </c>
-      <c r="C20" s="72">
+      <c r="C20" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D20" s="72">
+      <c r="D20" s="73">
         <f>"spring_phab_lwdeqvolm100|"&amp;'Metrics'!$C$20</f>
         <v/>
       </c>
-      <c r="E20" s="72">
+      <c r="E20" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$20,curve_key,0),MATCH("spring_phab_lwdeqvolm100|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F20" s="72">
+      <c r="F20" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="G20" s="72">
+      <c r="G20" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="H20" s="72">
+      <c r="H20" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="I20" s="72">
+      <c r="I20" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="J20" s="72">
+      <c r="J20" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="K20" s="72">
+      <c r="K20" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="L20" s="72">
+      <c r="L20" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="M20" s="72">
+      <c r="M20" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="N20" s="72">
+      <c r="N20" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="O20" s="72">
+      <c r="O20" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="P20" s="72">
+      <c r="P20" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="Q20" s="72">
+      <c r="Q20" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="R20" s="72">
+      <c r="R20" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="S20" s="72">
+      <c r="S20" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="T20" s="72">
+      <c r="T20" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="U20" s="72">
+      <c r="U20" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="V20" s="73">
+      <c r="V20" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$20),MAX(0,MIN(1,IF('Metrics'!$B$20&lt;='Metrics'!$F$20,'Metrics'!$N$20,IF('Metrics'!$B$20&gt;='Metrics'!$M$20,'Metrics'!$U$20,IF('Metrics'!$B$20&lt;='Metrics'!$G$20,IF('Metrics'!$G$20-'Metrics'!$F$20&lt;=0,'Metrics'!$O$20,'Metrics'!$N$20+('Metrics'!$B$20-'Metrics'!$F$20)/('Metrics'!$G$20-'Metrics'!$F$20)*('Metrics'!$O$20-'Metrics'!$N$20)),IF('Metrics'!$B$20&lt;='Metrics'!$H$20,IF('Metrics'!$H$20-'Metrics'!$G$20&lt;=0,'Metrics'!$P$20,'Metrics'!$O$20+('Metrics'!$B$20-'Metrics'!$G$20)/('Metrics'!$H$20-'Metrics'!$G$20)*('Metrics'!$P$20-'Metrics'!$O$20)),IF('Metrics'!$B$20&lt;='Metrics'!$I$20,IF('Metrics'!$I$20-'Metrics'!$H$20&lt;=0,'Metrics'!$Q$20,'Metrics'!$P$20+('Metrics'!$B$20-'Metrics'!$H$20)/('Metrics'!$I$20-'Metrics'!$H$20)*('Metrics'!$Q$20-'Metrics'!$P$20)),IF('Metrics'!$B$20&lt;='Metrics'!$J$20,IF('Metrics'!$J$20-'Metrics'!$I$20&lt;=0,'Metrics'!$R$20,'Metrics'!$Q$20+('Metrics'!$B$20-'Metrics'!$I$20)/('Metrics'!$J$20-'Metrics'!$I$20)*('Metrics'!$R$20-'Metrics'!$Q$20)),IF('Metrics'!$B$20&lt;='Metrics'!$K$20,IF('Metrics'!$K$20-'Metrics'!$J$20&lt;=0,'Metrics'!$S$20,'Metrics'!$R$20+('Metrics'!$B$20-'Metrics'!$J$20)/('Metrics'!$K$20-'Metrics'!$J$20)*('Metrics'!$S$20-'Metrics'!$R$20)),IF('Metrics'!$B$20&lt;='Metrics'!$L$20,IF('Metrics'!$L$20-'Metrics'!$K$20&lt;=0,'Metrics'!$T$20,'Metrics'!$S$20+('Metrics'!$B$20-'Metrics'!$K$20)/('Metrics'!$L$20-'Metrics'!$K$20)*('Metrics'!$T$20-'Metrics'!$S$20)),IF('Metrics'!$M$20-'Metrics'!$L$20&lt;=0,'Metrics'!$U$20,'Metrics'!$T$20+('Metrics'!$B$20-'Metrics'!$L$20)/('Metrics'!$M$20-'Metrics'!$L$20)*('Metrics'!$U$20-'Metrics'!$T$20)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Canopy density, mid-channel</t>
         </is>
       </c>
-      <c r="B21" s="72">
+      <c r="B21" s="73">
         <f>IF('DEEP Score'!$E$35="","",'DEEP Score'!$E$35)</f>
         <v/>
       </c>
-      <c r="C21" s="72">
+      <c r="C21" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D21" s="72">
+      <c r="D21" s="73">
         <f>"spring_phab_xcdenmid|"&amp;'Metrics'!$C$21</f>
         <v/>
       </c>
-      <c r="E21" s="72">
+      <c r="E21" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$21,curve_key,0),MATCH("spring_phab_xcdenmid|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F21" s="72">
+      <c r="F21" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="G21" s="72">
+      <c r="G21" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="H21" s="72">
+      <c r="H21" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="I21" s="72">
+      <c r="I21" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="J21" s="72">
+      <c r="J21" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="K21" s="72">
+      <c r="K21" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="L21" s="72">
+      <c r="L21" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="M21" s="72">
+      <c r="M21" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="N21" s="72">
+      <c r="N21" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="O21" s="72">
+      <c r="O21" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="P21" s="72">
+      <c r="P21" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="Q21" s="72">
+      <c r="Q21" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="R21" s="72">
+      <c r="R21" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="S21" s="72">
+      <c r="S21" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="T21" s="72">
+      <c r="T21" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="U21" s="72">
+      <c r="U21" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="V21" s="73">
+      <c r="V21" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$21),MAX(0,MIN(1,IF('Metrics'!$B$21&lt;='Metrics'!$F$21,'Metrics'!$N$21,IF('Metrics'!$B$21&gt;='Metrics'!$M$21,'Metrics'!$U$21,IF('Metrics'!$B$21&lt;='Metrics'!$G$21,IF('Metrics'!$G$21-'Metrics'!$F$21&lt;=0,'Metrics'!$O$21,'Metrics'!$N$21+('Metrics'!$B$21-'Metrics'!$F$21)/('Metrics'!$G$21-'Metrics'!$F$21)*('Metrics'!$O$21-'Metrics'!$N$21)),IF('Metrics'!$B$21&lt;='Metrics'!$H$21,IF('Metrics'!$H$21-'Metrics'!$G$21&lt;=0,'Metrics'!$P$21,'Metrics'!$O$21+('Metrics'!$B$21-'Metrics'!$G$21)/('Metrics'!$H$21-'Metrics'!$G$21)*('Metrics'!$P$21-'Metrics'!$O$21)),IF('Metrics'!$B$21&lt;='Metrics'!$I$21,IF('Metrics'!$I$21-'Metrics'!$H$21&lt;=0,'Metrics'!$Q$21,'Metrics'!$P$21+('Metrics'!$B$21-'Metrics'!$H$21)/('Metrics'!$I$21-'Metrics'!$H$21)*('Metrics'!$Q$21-'Metrics'!$P$21)),IF('Metrics'!$B$21&lt;='Metrics'!$J$21,IF('Metrics'!$J$21-'Metrics'!$I$21&lt;=0,'Metrics'!$R$21,'Metrics'!$Q$21+('Metrics'!$B$21-'Metrics'!$I$21)/('Metrics'!$J$21-'Metrics'!$I$21)*('Metrics'!$R$21-'Metrics'!$Q$21)),IF('Metrics'!$B$21&lt;='Metrics'!$K$21,IF('Metrics'!$K$21-'Metrics'!$J$21&lt;=0,'Metrics'!$S$21,'Metrics'!$R$21+('Metrics'!$B$21-'Metrics'!$J$21)/('Metrics'!$K$21-'Metrics'!$J$21)*('Metrics'!$S$21-'Metrics'!$R$21)),IF('Metrics'!$B$21&lt;='Metrics'!$L$21,IF('Metrics'!$L$21-'Metrics'!$K$21&lt;=0,'Metrics'!$T$21,'Metrics'!$S$21+('Metrics'!$B$21-'Metrics'!$K$21)/('Metrics'!$L$21-'Metrics'!$K$21)*('Metrics'!$T$21-'Metrics'!$S$21)),IF('Metrics'!$M$21-'Metrics'!$L$21&lt;=0,'Metrics'!$U$21,'Metrics'!$T$21+('Metrics'!$B$21-'Metrics'!$L$21)/('Metrics'!$M$21-'Metrics'!$L$21)*('Metrics'!$U$21-'Metrics'!$T$21)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>Riparian veg cover, woody</t>
         </is>
       </c>
-      <c r="B22" s="72">
+      <c r="B22" s="73">
         <f>IF('DEEP Score'!$E$36="","",'DEEP Score'!$E$36)</f>
         <v/>
       </c>
-      <c r="C22" s="72">
+      <c r="C22" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D22" s="72">
+      <c r="D22" s="73">
         <f>"spring_phab_xcmgw|"&amp;'Metrics'!$C$22</f>
         <v/>
       </c>
-      <c r="E22" s="72">
+      <c r="E22" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$22,curve_key,0),MATCH("spring_phab_xcmgw|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F22" s="72">
+      <c r="F22" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="G22" s="72">
+      <c r="G22" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="H22" s="72">
+      <c r="H22" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="I22" s="72">
+      <c r="I22" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="J22" s="72">
+      <c r="J22" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="K22" s="72">
+      <c r="K22" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="L22" s="72">
+      <c r="L22" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="M22" s="72">
+      <c r="M22" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="N22" s="72">
+      <c r="N22" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="O22" s="72">
+      <c r="O22" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="P22" s="72">
+      <c r="P22" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="Q22" s="72">
+      <c r="Q22" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="R22" s="72">
+      <c r="R22" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="S22" s="72">
+      <c r="S22" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="T22" s="72">
+      <c r="T22" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="U22" s="72">
+      <c r="U22" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="V22" s="73">
+      <c r="V22" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$22),MAX(0,MIN(1,IF('Metrics'!$B$22&lt;='Metrics'!$F$22,'Metrics'!$N$22,IF('Metrics'!$B$22&gt;='Metrics'!$M$22,'Metrics'!$U$22,IF('Metrics'!$B$22&lt;='Metrics'!$G$22,IF('Metrics'!$G$22-'Metrics'!$F$22&lt;=0,'Metrics'!$O$22,'Metrics'!$N$22+('Metrics'!$B$22-'Metrics'!$F$22)/('Metrics'!$G$22-'Metrics'!$F$22)*('Metrics'!$O$22-'Metrics'!$N$22)),IF('Metrics'!$B$22&lt;='Metrics'!$H$22,IF('Metrics'!$H$22-'Metrics'!$G$22&lt;=0,'Metrics'!$P$22,'Metrics'!$O$22+('Metrics'!$B$22-'Metrics'!$G$22)/('Metrics'!$H$22-'Metrics'!$G$22)*('Metrics'!$P$22-'Metrics'!$O$22)),IF('Metrics'!$B$22&lt;='Metrics'!$I$22,IF('Metrics'!$I$22-'Metrics'!$H$22&lt;=0,'Metrics'!$Q$22,'Metrics'!$P$22+('Metrics'!$B$22-'Metrics'!$H$22)/('Metrics'!$I$22-'Metrics'!$H$22)*('Metrics'!$Q$22-'Metrics'!$P$22)),IF('Metrics'!$B$22&lt;='Metrics'!$J$22,IF('Metrics'!$J$22-'Metrics'!$I$22&lt;=0,'Metrics'!$R$22,'Metrics'!$Q$22+('Metrics'!$B$22-'Metrics'!$I$22)/('Metrics'!$J$22-'Metrics'!$I$22)*('Metrics'!$R$22-'Metrics'!$Q$22)),IF('Metrics'!$B$22&lt;='Metrics'!$K$22,IF('Metrics'!$K$22-'Metrics'!$J$22&lt;=0,'Metrics'!$S$22,'Metrics'!$R$22+('Metrics'!$B$22-'Metrics'!$J$22)/('Metrics'!$K$22-'Metrics'!$J$22)*('Metrics'!$S$22-'Metrics'!$R$22)),IF('Metrics'!$B$22&lt;='Metrics'!$L$22,IF('Metrics'!$L$22-'Metrics'!$K$22&lt;=0,'Metrics'!$T$22,'Metrics'!$S$22+('Metrics'!$B$22-'Metrics'!$K$22)/('Metrics'!$L$22-'Metrics'!$K$22)*('Metrics'!$T$22-'Metrics'!$S$22)),IF('Metrics'!$M$22-'Metrics'!$L$22&lt;=0,'Metrics'!$U$22,'Metrics'!$T$22+('Metrics'!$B$22-'Metrics'!$L$22)/('Metrics'!$M$22-'Metrics'!$L$22)*('Metrics'!$U$22-'Metrics'!$T$22)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>Fast-water / riffle habitat</t>
         </is>
       </c>
-      <c r="B23" s="72">
+      <c r="B23" s="73">
         <f>IF('DEEP Score'!$E$37="","",'DEEP Score'!$E$37)</f>
         <v/>
       </c>
-      <c r="C23" s="72">
+      <c r="C23" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D23" s="72">
+      <c r="D23" s="73">
         <f>"spring_phab_pct_fast|"&amp;'Metrics'!$C$23</f>
         <v/>
       </c>
-      <c r="E23" s="72">
+      <c r="E23" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$23,curve_key,0),MATCH("spring_phab_pct_fast|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F23" s="72">
+      <c r="F23" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="G23" s="72">
+      <c r="G23" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="H23" s="72">
+      <c r="H23" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="I23" s="72">
+      <c r="I23" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="J23" s="72">
+      <c r="J23" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="K23" s="72">
+      <c r="K23" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="L23" s="72">
+      <c r="L23" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="M23" s="72">
+      <c r="M23" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="N23" s="72">
+      <c r="N23" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="O23" s="72">
+      <c r="O23" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="P23" s="72">
+      <c r="P23" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="Q23" s="72">
+      <c r="Q23" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="R23" s="72">
+      <c r="R23" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="S23" s="72">
+      <c r="S23" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="T23" s="72">
+      <c r="T23" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="U23" s="72">
+      <c r="U23" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="V23" s="73">
+      <c r="V23" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$23),MAX(0,MIN(1,IF('Metrics'!$B$23&lt;='Metrics'!$F$23,'Metrics'!$N$23,IF('Metrics'!$B$23&gt;='Metrics'!$M$23,'Metrics'!$U$23,IF('Metrics'!$B$23&lt;='Metrics'!$G$23,IF('Metrics'!$G$23-'Metrics'!$F$23&lt;=0,'Metrics'!$O$23,'Metrics'!$N$23+('Metrics'!$B$23-'Metrics'!$F$23)/('Metrics'!$G$23-'Metrics'!$F$23)*('Metrics'!$O$23-'Metrics'!$N$23)),IF('Metrics'!$B$23&lt;='Metrics'!$H$23,IF('Metrics'!$H$23-'Metrics'!$G$23&lt;=0,'Metrics'!$P$23,'Metrics'!$O$23+('Metrics'!$B$23-'Metrics'!$G$23)/('Metrics'!$H$23-'Metrics'!$G$23)*('Metrics'!$P$23-'Metrics'!$O$23)),IF('Metrics'!$B$23&lt;='Metrics'!$I$23,IF('Metrics'!$I$23-'Metrics'!$H$23&lt;=0,'Metrics'!$Q$23,'Metrics'!$P$23+('Metrics'!$B$23-'Metrics'!$H$23)/('Metrics'!$I$23-'Metrics'!$H$23)*('Metrics'!$Q$23-'Metrics'!$P$23)),IF('Metrics'!$B$23&lt;='Metrics'!$J$23,IF('Metrics'!$J$23-'Metrics'!$I$23&lt;=0,'Metrics'!$R$23,'Metrics'!$Q$23+('Metrics'!$B$23-'Metrics'!$I$23)/('Metrics'!$J$23-'Metrics'!$I$23)*('Metrics'!$R$23-'Metrics'!$Q$23)),IF('Metrics'!$B$23&lt;='Metrics'!$K$23,IF('Metrics'!$K$23-'Metrics'!$J$23&lt;=0,'Metrics'!$S$23,'Metrics'!$R$23+('Metrics'!$B$23-'Metrics'!$J$23)/('Metrics'!$K$23-'Metrics'!$J$23)*('Metrics'!$S$23-'Metrics'!$R$23)),IF('Metrics'!$B$23&lt;='Metrics'!$L$23,IF('Metrics'!$L$23-'Metrics'!$K$23&lt;=0,'Metrics'!$T$23,'Metrics'!$S$23+('Metrics'!$B$23-'Metrics'!$K$23)/('Metrics'!$L$23-'Metrics'!$K$23)*('Metrics'!$T$23-'Metrics'!$S$23)),IF('Metrics'!$M$23-'Metrics'!$L$23&lt;=0,'Metrics'!$U$23,'Metrics'!$T$23+('Metrics'!$B$23-'Metrics'!$L$23)/('Metrics'!$M$23-'Metrics'!$L$23)*('Metrics'!$U$23-'Metrics'!$T$23)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>Natural fish cover</t>
         </is>
       </c>
-      <c r="B24" s="72">
+      <c r="B24" s="73">
         <f>IF('DEEP Score'!$E$38="","",'DEEP Score'!$E$38)</f>
         <v/>
       </c>
-      <c r="C24" s="72">
+      <c r="C24" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D24" s="72">
+      <c r="D24" s="73">
         <f>"spring_phab_xfc_nat|"&amp;'Metrics'!$C$24</f>
         <v/>
       </c>
-      <c r="E24" s="72">
+      <c r="E24" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$24,curve_key,0),MATCH("spring_phab_xfc_nat|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F24" s="72">
+      <c r="F24" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="G24" s="72">
+      <c r="G24" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="H24" s="72">
+      <c r="H24" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="I24" s="72">
+      <c r="I24" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="J24" s="72">
+      <c r="J24" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="K24" s="72">
+      <c r="K24" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="L24" s="72">
+      <c r="L24" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="M24" s="72">
+      <c r="M24" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="N24" s="72">
+      <c r="N24" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="O24" s="72">
+      <c r="O24" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="P24" s="72">
+      <c r="P24" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="Q24" s="72">
+      <c r="Q24" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="R24" s="72">
+      <c r="R24" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="S24" s="72">
+      <c r="S24" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="T24" s="72">
+      <c r="T24" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="U24" s="72">
+      <c r="U24" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="V24" s="73">
+      <c r="V24" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$24),MAX(0,MIN(1,IF('Metrics'!$B$24&lt;='Metrics'!$F$24,'Metrics'!$N$24,IF('Metrics'!$B$24&gt;='Metrics'!$M$24,'Metrics'!$U$24,IF('Metrics'!$B$24&lt;='Metrics'!$G$24,IF('Metrics'!$G$24-'Metrics'!$F$24&lt;=0,'Metrics'!$O$24,'Metrics'!$N$24+('Metrics'!$B$24-'Metrics'!$F$24)/('Metrics'!$G$24-'Metrics'!$F$24)*('Metrics'!$O$24-'Metrics'!$N$24)),IF('Metrics'!$B$24&lt;='Metrics'!$H$24,IF('Metrics'!$H$24-'Metrics'!$G$24&lt;=0,'Metrics'!$P$24,'Metrics'!$O$24+('Metrics'!$B$24-'Metrics'!$G$24)/('Metrics'!$H$24-'Metrics'!$G$24)*('Metrics'!$P$24-'Metrics'!$O$24)),IF('Metrics'!$B$24&lt;='Metrics'!$I$24,IF('Metrics'!$I$24-'Metrics'!$H$24&lt;=0,'Metrics'!$Q$24,'Metrics'!$P$24+('Metrics'!$B$24-'Metrics'!$H$24)/('Metrics'!$I$24-'Metrics'!$H$24)*('Metrics'!$Q$24-'Metrics'!$P$24)),IF('Metrics'!$B$24&lt;='Metrics'!$J$24,IF('Metrics'!$J$24-'Metrics'!$I$24&lt;=0,'Metrics'!$R$24,'Metrics'!$Q$24+('Metrics'!$B$24-'Metrics'!$I$24)/('Metrics'!$J$24-'Metrics'!$I$24)*('Metrics'!$R$24-'Metrics'!$Q$24)),IF('Metrics'!$B$24&lt;='Metrics'!$K$24,IF('Metrics'!$K$24-'Metrics'!$J$24&lt;=0,'Metrics'!$S$24,'Metrics'!$R$24+('Metrics'!$B$24-'Metrics'!$J$24)/('Metrics'!$K$24-'Metrics'!$J$24)*('Metrics'!$S$24-'Metrics'!$R$24)),IF('Metrics'!$B$24&lt;='Metrics'!$L$24,IF('Metrics'!$L$24-'Metrics'!$K$24&lt;=0,'Metrics'!$T$24,'Metrics'!$S$24+('Metrics'!$B$24-'Metrics'!$K$24)/('Metrics'!$L$24-'Metrics'!$K$24)*('Metrics'!$T$24-'Metrics'!$S$24)),IF('Metrics'!$M$24-'Metrics'!$L$24&lt;=0,'Metrics'!$U$24,'Metrics'!$T$24+('Metrics'!$B$24-'Metrics'!$L$24)/('Metrics'!$M$24-'Metrics'!$L$24)*('Metrics'!$U$24-'Metrics'!$T$24)))))))))))),"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="inlineStr">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>Mapped dams within one mile</t>
         </is>
       </c>
-      <c r="B25" s="72">
+      <c r="B25" s="73">
         <f>IF('DEEP Score'!$E$39="","",'DEEP Score'!$E$39)</f>
         <v/>
       </c>
-      <c r="C25" s="72">
+      <c r="C25" s="73">
         <f>""</f>
         <v/>
       </c>
-      <c r="D25" s="72">
+      <c r="D25" s="73">
         <f>"spring_nid_dams_1mi|"&amp;'Metrics'!$C$25</f>
         <v/>
       </c>
-      <c r="E25" s="72">
+      <c r="E25" s="73">
         <f>IFERROR(MATCH('Metrics'!$D$25,curve_key,0),MATCH("spring_nid_dams_1mi|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F25" s="72">
+      <c r="F25" s="73">
         <f>INDEX(curve_x1,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="G25" s="72">
+      <c r="G25" s="73">
         <f>INDEX(curve_x2,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="H25" s="72">
+      <c r="H25" s="73">
         <f>INDEX(curve_x3,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="I25" s="72">
+      <c r="I25" s="73">
         <f>INDEX(curve_x4,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="J25" s="72">
+      <c r="J25" s="73">
         <f>INDEX(curve_x5,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="K25" s="72">
+      <c r="K25" s="73">
         <f>INDEX(curve_x6,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="L25" s="72">
+      <c r="L25" s="73">
         <f>INDEX(curve_x7,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="M25" s="72">
+      <c r="M25" s="73">
         <f>INDEX(curve_x8,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="N25" s="72">
+      <c r="N25" s="73">
         <f>INDEX(curve_y1,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="O25" s="72">
+      <c r="O25" s="73">
         <f>INDEX(curve_y2,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="P25" s="72">
+      <c r="P25" s="73">
         <f>INDEX(curve_y3,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="Q25" s="72">
+      <c r="Q25" s="73">
         <f>INDEX(curve_y4,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="R25" s="72">
+      <c r="R25" s="73">
         <f>INDEX(curve_y5,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="S25" s="72">
+      <c r="S25" s="73">
         <f>INDEX(curve_y6,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="T25" s="72">
+      <c r="T25" s="73">
         <f>INDEX(curve_y7,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="U25" s="72">
+      <c r="U25" s="73">
         <f>INDEX(curve_y8,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="V25" s="73">
+      <c r="V25" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$25),MAX(0,MIN(1,IF('Metrics'!$B$25&lt;='Metrics'!$F$25,'Metrics'!$N$25,IF('Metrics'!$B$25&gt;='Metrics'!$M$25,'Metrics'!$U$25,IF('Metrics'!$B$25&lt;='Metrics'!$G$25,IF('Metrics'!$G$25-'Metrics'!$F$25&lt;=0,'Metrics'!$O$25,'Metrics'!$N$25+('Metrics'!$B$25-'Metrics'!$F$25)/('Metrics'!$G$25-'Metrics'!$F$25)*('Metrics'!$O$25-'Metrics'!$N$25)),IF('Metrics'!$B$25&lt;='Metrics'!$H$25,IF('Metrics'!$H$25-'Metrics'!$G$25&lt;=0,'Metrics'!$P$25,'Metrics'!$O$25+('Metrics'!$B$25-'Metrics'!$G$25)/('Metrics'!$H$25-'Metrics'!$G$25)*('Metrics'!$P$25-'Metrics'!$O$25)),IF('Metrics'!$B$25&lt;='Metrics'!$I$25,IF('Metrics'!$I$25-'Metrics'!$H$25&lt;=0,'Metrics'!$Q$25,'Metrics'!$P$25+('Metrics'!$B$25-'Metrics'!$H$25)/('Metrics'!$I$25-'Metrics'!$H$25)*('Metrics'!$Q$25-'Metrics'!$P$25)),IF('Metrics'!$B$25&lt;='Metrics'!$J$25,IF('Metrics'!$J$25-'Metrics'!$I$25&lt;=0,'Metrics'!$R$25,'Metrics'!$Q$25+('Metrics'!$B$25-'Metrics'!$I$25)/('Metrics'!$J$25-'Metrics'!$I$25)*('Metrics'!$R$25-'Metrics'!$Q$25)),IF('Metrics'!$B$25&lt;='Metrics'!$K$25,IF('Metrics'!$K$25-'Metrics'!$J$25&lt;=0,'Metrics'!$S$25,'Metrics'!$R$25+('Metrics'!$B$25-'Metrics'!$J$25)/('Metrics'!$K$25-'Metrics'!$J$25)*('Metrics'!$S$25-'Metrics'!$R$25)),IF('Metrics'!$B$25&lt;='Metrics'!$L$25,IF('Metrics'!$L$25-'Metrics'!$K$25&lt;=0,'Metrics'!$T$25,'Metrics'!$S$25+('Metrics'!$B$25-'Metrics'!$K$25)/('Metrics'!$L$25-'Metrics'!$K$25)*('Metrics'!$T$25-'Metrics'!$S$25)),IF('Metrics'!$M$25-'Metrics'!$L$25&lt;=0,'Metrics'!$U$25,'Metrics'!$T$25+('Metrics'!$B$25-'Metrics'!$L$25)/('Metrics'!$M$25-'Metrics'!$L$25)*('Metrics'!$U$25-'Metrics'!$T$25)))))))))))),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
+  <mergeCells count="1">
+    <mergeCell ref="A3:D3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5037,825 +5112,825 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="71" t="inlineStr">
+      <c r="A1" s="72" t="inlineStr">
         <is>
           <t>Function scores and the outcome rollup</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Physical weight</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Chemical weight</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Biological weight</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Physical weighted</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Chemical weighted</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Biological weighted</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>Physical maximum</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>Chemical maximum</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>Biological maximum</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Catchment hydrology</t>
         </is>
       </c>
-      <c r="B4" s="72">
+      <c r="B4" s="73">
         <f>IF(COUNT('DEEP Score'!G12:G13)=0,"",SUM('DEEP Score'!G12:G13)/COUNT('DEEP Score'!G12:G13)*15)</f>
         <v/>
       </c>
-      <c r="C4" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="38" t="n">
+      <c r="C4" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E4" s="38" t="n">
+      <c r="E4" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F4" s="72">
+      <c r="F4" s="73">
         <f>IF(ISNUMBER('Results'!$B$4),'Results'!$B$4*'Results'!$C$4,0)</f>
         <v/>
       </c>
-      <c r="G4" s="72">
+      <c r="G4" s="73">
         <f>IF(ISNUMBER('Results'!$B$4),'Results'!$B$4*'Results'!$D$4,0)</f>
         <v/>
       </c>
-      <c r="H4" s="72">
+      <c r="H4" s="73">
         <f>IF(ISNUMBER('Results'!$B$4),'Results'!$B$4*'Results'!$E$4,0)</f>
         <v/>
       </c>
-      <c r="I4" s="72">
+      <c r="I4" s="73">
         <f>IF(ISNUMBER('Results'!$B$4),15*'Results'!$C$4,0)</f>
         <v/>
       </c>
-      <c r="J4" s="72">
+      <c r="J4" s="73">
         <f>IF(ISNUMBER('Results'!$B$4),15*'Results'!$D$4,0)</f>
         <v/>
       </c>
-      <c r="K4" s="72">
+      <c r="K4" s="73">
         <f>IF(ISNUMBER('Results'!$B$4),15*'Results'!$E$4,0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>Surface water storage</t>
         </is>
       </c>
-      <c r="B5" s="72">
+      <c r="B5" s="73">
         <f>IF(COUNT('DEEP Score'!G14:G14)=0,"",SUM('DEEP Score'!G14:G14)/COUNT('DEEP Score'!G14:G14)*15)</f>
         <v/>
       </c>
-      <c r="C5" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="38" t="n">
+      <c r="C5" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" s="72">
+      <c r="F5" s="73">
         <f>IF(ISNUMBER('Results'!$B$5),'Results'!$B$5*'Results'!$C$5,0)</f>
         <v/>
       </c>
-      <c r="G5" s="72">
+      <c r="G5" s="73">
         <f>IF(ISNUMBER('Results'!$B$5),'Results'!$B$5*'Results'!$D$5,0)</f>
         <v/>
       </c>
-      <c r="H5" s="72">
+      <c r="H5" s="73">
         <f>IF(ISNUMBER('Results'!$B$5),'Results'!$B$5*'Results'!$E$5,0)</f>
         <v/>
       </c>
-      <c r="I5" s="72">
+      <c r="I5" s="73">
         <f>IF(ISNUMBER('Results'!$B$5),15*'Results'!$C$5,0)</f>
         <v/>
       </c>
-      <c r="J5" s="72">
+      <c r="J5" s="73">
         <f>IF(ISNUMBER('Results'!$B$5),15*'Results'!$D$5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="72">
+      <c r="K5" s="73">
         <f>IF(ISNUMBER('Results'!$B$5),15*'Results'!$E$5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>Reach inflow</t>
         </is>
       </c>
-      <c r="B6" s="72">
+      <c r="B6" s="73">
         <f>IF(COUNT('DEEP Score'!G15:G15)=0,"",SUM('DEEP Score'!G15:G15)/COUNT('DEEP Score'!G15:G15)*15)</f>
         <v/>
       </c>
-      <c r="C6" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="38" t="n">
+      <c r="C6" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F6" s="72">
+      <c r="F6" s="73">
         <f>IF(ISNUMBER('Results'!$B$6),'Results'!$B$6*'Results'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="G6" s="72">
+      <c r="G6" s="73">
         <f>IF(ISNUMBER('Results'!$B$6),'Results'!$B$6*'Results'!$D$6,0)</f>
         <v/>
       </c>
-      <c r="H6" s="72">
+      <c r="H6" s="73">
         <f>IF(ISNUMBER('Results'!$B$6),'Results'!$B$6*'Results'!$E$6,0)</f>
         <v/>
       </c>
-      <c r="I6" s="72">
+      <c r="I6" s="73">
         <f>IF(ISNUMBER('Results'!$B$6),15*'Results'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J6" s="72">
+      <c r="J6" s="73">
         <f>IF(ISNUMBER('Results'!$B$6),15*'Results'!$D$6,0)</f>
         <v/>
       </c>
-      <c r="K6" s="72">
+      <c r="K6" s="73">
         <f>IF(ISNUMBER('Results'!$B$6),15*'Results'!$E$6,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>Streamflow regime</t>
         </is>
       </c>
-      <c r="B7" s="72">
+      <c r="B7" s="73">
         <f>IF(COUNT('DEEP Score'!G16:G17)=0,"",SUM('DEEP Score'!G16:G17)/COUNT('DEEP Score'!G16:G17)*15)</f>
         <v/>
       </c>
-      <c r="C7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="38" t="n">
+      <c r="C7" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E7" s="38" t="n">
+      <c r="E7" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F7" s="72">
+      <c r="F7" s="73">
         <f>IF(ISNUMBER('Results'!$B$7),'Results'!$B$7*'Results'!$C$7,0)</f>
         <v/>
       </c>
-      <c r="G7" s="72">
+      <c r="G7" s="73">
         <f>IF(ISNUMBER('Results'!$B$7),'Results'!$B$7*'Results'!$D$7,0)</f>
         <v/>
       </c>
-      <c r="H7" s="72">
+      <c r="H7" s="73">
         <f>IF(ISNUMBER('Results'!$B$7),'Results'!$B$7*'Results'!$E$7,0)</f>
         <v/>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="73">
         <f>IF(ISNUMBER('Results'!$B$7),15*'Results'!$C$7,0)</f>
         <v/>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="73">
         <f>IF(ISNUMBER('Results'!$B$7),15*'Results'!$D$7,0)</f>
         <v/>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="73">
         <f>IF(ISNUMBER('Results'!$B$7),15*'Results'!$E$7,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>Low flow and baseflow dynamics</t>
         </is>
       </c>
-      <c r="B8" s="72">
+      <c r="B8" s="73">
         <f>IF(COUNT('DEEP Score'!G18:G20)=0,"",SUM('DEEP Score'!G18:G20)/COUNT('DEEP Score'!G18:G20)*15)</f>
         <v/>
       </c>
-      <c r="C8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="38" t="n">
+      <c r="C8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="38" t="n">
+      <c r="E8" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="72">
+      <c r="F8" s="73">
         <f>IF(ISNUMBER('Results'!$B$8),'Results'!$B$8*'Results'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G8" s="72">
+      <c r="G8" s="73">
         <f>IF(ISNUMBER('Results'!$B$8),'Results'!$B$8*'Results'!$D$8,0)</f>
         <v/>
       </c>
-      <c r="H8" s="72">
+      <c r="H8" s="73">
         <f>IF(ISNUMBER('Results'!$B$8),'Results'!$B$8*'Results'!$E$8,0)</f>
         <v/>
       </c>
-      <c r="I8" s="72">
+      <c r="I8" s="73">
         <f>IF(ISNUMBER('Results'!$B$8),15*'Results'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="J8" s="72">
+      <c r="J8" s="73">
         <f>IF(ISNUMBER('Results'!$B$8),15*'Results'!$D$8,0)</f>
         <v/>
       </c>
-      <c r="K8" s="72">
+      <c r="K8" s="73">
         <f>IF(ISNUMBER('Results'!$B$8),15*'Results'!$E$8,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>High flow dynamics</t>
         </is>
       </c>
-      <c r="B9" s="72">
+      <c r="B9" s="73">
         <f>IF(COUNT('DEEP Score'!G21:G21)=0,"",SUM('DEEP Score'!G21:G21)/COUNT('DEEP Score'!G21:G21)*15)</f>
         <v/>
       </c>
-      <c r="C9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="38" t="n">
+      <c r="C9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E9" s="38" t="n">
+      <c r="E9" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F9" s="72">
+      <c r="F9" s="73">
         <f>IF(ISNUMBER('Results'!$B$9),'Results'!$B$9*'Results'!$C$9,0)</f>
         <v/>
       </c>
-      <c r="G9" s="72">
+      <c r="G9" s="73">
         <f>IF(ISNUMBER('Results'!$B$9),'Results'!$B$9*'Results'!$D$9,0)</f>
         <v/>
       </c>
-      <c r="H9" s="72">
+      <c r="H9" s="73">
         <f>IF(ISNUMBER('Results'!$B$9),'Results'!$B$9*'Results'!$E$9,0)</f>
         <v/>
       </c>
-      <c r="I9" s="72">
+      <c r="I9" s="73">
         <f>IF(ISNUMBER('Results'!$B$9),15*'Results'!$C$9,0)</f>
         <v/>
       </c>
-      <c r="J9" s="72">
+      <c r="J9" s="73">
         <f>IF(ISNUMBER('Results'!$B$9),15*'Results'!$D$9,0)</f>
         <v/>
       </c>
-      <c r="K9" s="72">
+      <c r="K9" s="73">
         <f>IF(ISNUMBER('Results'!$B$9),15*'Results'!$E$9,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Floodplain connectivity</t>
         </is>
       </c>
-      <c r="B10" s="72">
+      <c r="B10" s="73">
         <f>IF(COUNT('DEEP Score'!G22:G23)=0,"",SUM('DEEP Score'!G22:G23)/COUNT('DEEP Score'!G22:G23)*15)</f>
         <v/>
       </c>
-      <c r="C10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="38" t="n">
+      <c r="C10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E10" s="38" t="n">
+      <c r="E10" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F10" s="72">
+      <c r="F10" s="73">
         <f>IF(ISNUMBER('Results'!$B$10),'Results'!$B$10*'Results'!$C$10,0)</f>
         <v/>
       </c>
-      <c r="G10" s="72">
+      <c r="G10" s="73">
         <f>IF(ISNUMBER('Results'!$B$10),'Results'!$B$10*'Results'!$D$10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="72">
+      <c r="H10" s="73">
         <f>IF(ISNUMBER('Results'!$B$10),'Results'!$B$10*'Results'!$E$10,0)</f>
         <v/>
       </c>
-      <c r="I10" s="72">
+      <c r="I10" s="73">
         <f>IF(ISNUMBER('Results'!$B$10),15*'Results'!$C$10,0)</f>
         <v/>
       </c>
-      <c r="J10" s="72">
+      <c r="J10" s="73">
         <f>IF(ISNUMBER('Results'!$B$10),15*'Results'!$D$10,0)</f>
         <v/>
       </c>
-      <c r="K10" s="72">
+      <c r="K10" s="73">
         <f>IF(ISNUMBER('Results'!$B$10),15*'Results'!$E$10,0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>Hyporheic connectivity</t>
         </is>
       </c>
-      <c r="B11" s="72">
+      <c r="B11" s="73">
         <f>IF(COUNT('DEEP Score'!G24:G25)=0,"",SUM('DEEP Score'!G24:G25)/COUNT('DEEP Score'!G24:G25)*15)</f>
         <v/>
       </c>
-      <c r="C11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="38" t="n">
+      <c r="C11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="38" t="n">
+      <c r="E11" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F11" s="72">
+      <c r="F11" s="73">
         <f>IF(ISNUMBER('Results'!$B$11),'Results'!$B$11*'Results'!$C$11,0)</f>
         <v/>
       </c>
-      <c r="G11" s="72">
+      <c r="G11" s="73">
         <f>IF(ISNUMBER('Results'!$B$11),'Results'!$B$11*'Results'!$D$11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="72">
+      <c r="H11" s="73">
         <f>IF(ISNUMBER('Results'!$B$11),'Results'!$B$11*'Results'!$E$11,0)</f>
         <v/>
       </c>
-      <c r="I11" s="72">
+      <c r="I11" s="73">
         <f>IF(ISNUMBER('Results'!$B$11),15*'Results'!$C$11,0)</f>
         <v/>
       </c>
-      <c r="J11" s="72">
+      <c r="J11" s="73">
         <f>IF(ISNUMBER('Results'!$B$11),15*'Results'!$D$11,0)</f>
         <v/>
       </c>
-      <c r="K11" s="72">
+      <c r="K11" s="73">
         <f>IF(ISNUMBER('Results'!$B$11),15*'Results'!$E$11,0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Channel evolution</t>
         </is>
       </c>
-      <c r="B12" s="72">
+      <c r="B12" s="73">
         <f>IF(COUNT('DEEP Score'!G26:G27)=0,"",SUM('DEEP Score'!G26:G27)/COUNT('DEEP Score'!G26:G27)*15)</f>
         <v/>
       </c>
-      <c r="C12" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="38" t="n">
+      <c r="C12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E12" s="38" t="n">
+      <c r="E12" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F12" s="72">
+      <c r="F12" s="73">
         <f>IF(ISNUMBER('Results'!$B$12),'Results'!$B$12*'Results'!$C$12,0)</f>
         <v/>
       </c>
-      <c r="G12" s="72">
+      <c r="G12" s="73">
         <f>IF(ISNUMBER('Results'!$B$12),'Results'!$B$12*'Results'!$D$12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="72">
+      <c r="H12" s="73">
         <f>IF(ISNUMBER('Results'!$B$12),'Results'!$B$12*'Results'!$E$12,0)</f>
         <v/>
       </c>
-      <c r="I12" s="72">
+      <c r="I12" s="73">
         <f>IF(ISNUMBER('Results'!$B$12),15*'Results'!$C$12,0)</f>
         <v/>
       </c>
-      <c r="J12" s="72">
+      <c r="J12" s="73">
         <f>IF(ISNUMBER('Results'!$B$12),15*'Results'!$D$12,0)</f>
         <v/>
       </c>
-      <c r="K12" s="72">
+      <c r="K12" s="73">
         <f>IF(ISNUMBER('Results'!$B$12),15*'Results'!$E$12,0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>Channel and floodplain dynamics</t>
         </is>
       </c>
-      <c r="B13" s="72">
+      <c r="B13" s="73">
         <f>IF(COUNT('DEEP Score'!G28:G29)=0,"",SUM('DEEP Score'!G28:G29)/COUNT('DEEP Score'!G28:G29)*15)</f>
         <v/>
       </c>
-      <c r="C13" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="38" t="n">
+      <c r="C13" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E13" s="38" t="n">
+      <c r="E13" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F13" s="72">
+      <c r="F13" s="73">
         <f>IF(ISNUMBER('Results'!$B$13),'Results'!$B$13*'Results'!$C$13,0)</f>
         <v/>
       </c>
-      <c r="G13" s="72">
+      <c r="G13" s="73">
         <f>IF(ISNUMBER('Results'!$B$13),'Results'!$B$13*'Results'!$D$13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="72">
+      <c r="H13" s="73">
         <f>IF(ISNUMBER('Results'!$B$13),'Results'!$B$13*'Results'!$E$13,0)</f>
         <v/>
       </c>
-      <c r="I13" s="72">
+      <c r="I13" s="73">
         <f>IF(ISNUMBER('Results'!$B$13),15*'Results'!$C$13,0)</f>
         <v/>
       </c>
-      <c r="J13" s="72">
+      <c r="J13" s="73">
         <f>IF(ISNUMBER('Results'!$B$13),15*'Results'!$D$13,0)</f>
         <v/>
       </c>
-      <c r="K13" s="72">
+      <c r="K13" s="73">
         <f>IF(ISNUMBER('Results'!$B$13),15*'Results'!$E$13,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>Sediment continuity</t>
         </is>
       </c>
-      <c r="B14" s="72">
+      <c r="B14" s="73">
         <f>IF(COUNT('DEEP Score'!G30:G31)=0,"",SUM('DEEP Score'!G30:G31)/COUNT('DEEP Score'!G30:G31)*15)</f>
         <v/>
       </c>
-      <c r="C14" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="38" t="n">
+      <c r="C14" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E14" s="38" t="n">
+      <c r="E14" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F14" s="72">
+      <c r="F14" s="73">
         <f>IF(ISNUMBER('Results'!$B$14),'Results'!$B$14*'Results'!$C$14,0)</f>
         <v/>
       </c>
-      <c r="G14" s="72">
+      <c r="G14" s="73">
         <f>IF(ISNUMBER('Results'!$B$14),'Results'!$B$14*'Results'!$D$14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="72">
+      <c r="H14" s="73">
         <f>IF(ISNUMBER('Results'!$B$14),'Results'!$B$14*'Results'!$E$14,0)</f>
         <v/>
       </c>
-      <c r="I14" s="72">
+      <c r="I14" s="73">
         <f>IF(ISNUMBER('Results'!$B$14),15*'Results'!$C$14,0)</f>
         <v/>
       </c>
-      <c r="J14" s="72">
+      <c r="J14" s="73">
         <f>IF(ISNUMBER('Results'!$B$14),15*'Results'!$D$14,0)</f>
         <v/>
       </c>
-      <c r="K14" s="72">
+      <c r="K14" s="73">
         <f>IF(ISNUMBER('Results'!$B$14),15*'Results'!$E$14,0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>Bed composition and bedform dynamics</t>
         </is>
       </c>
-      <c r="B15" s="72">
+      <c r="B15" s="73">
         <f>IF(COUNT('DEEP Score'!G32:G34)=0,"",SUM('DEEP Score'!G32:G34)/COUNT('DEEP Score'!G32:G34)*15)</f>
         <v/>
       </c>
-      <c r="C15" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="38" t="n">
+      <c r="C15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="E15" s="38" t="n">
+      <c r="E15" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F15" s="72">
+      <c r="F15" s="73">
         <f>IF(ISNUMBER('Results'!$B$15),'Results'!$B$15*'Results'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="G15" s="72">
+      <c r="G15" s="73">
         <f>IF(ISNUMBER('Results'!$B$15),'Results'!$B$15*'Results'!$D$15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="72">
+      <c r="H15" s="73">
         <f>IF(ISNUMBER('Results'!$B$15),'Results'!$B$15*'Results'!$E$15,0)</f>
         <v/>
       </c>
-      <c r="I15" s="72">
+      <c r="I15" s="73">
         <f>IF(ISNUMBER('Results'!$B$15),15*'Results'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="J15" s="72">
+      <c r="J15" s="73">
         <f>IF(ISNUMBER('Results'!$B$15),15*'Results'!$D$15,0)</f>
         <v/>
       </c>
-      <c r="K15" s="72">
+      <c r="K15" s="73">
         <f>IF(ISNUMBER('Results'!$B$15),15*'Results'!$E$15,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Light &amp; thermal regime</t>
         </is>
       </c>
-      <c r="B16" s="72">
+      <c r="B16" s="73">
         <f>IF(COUNT('DEEP Score'!G35:G35)=0,"",SUM('DEEP Score'!G35:G35)/COUNT('DEEP Score'!G35:G35)*15)</f>
         <v/>
       </c>
-      <c r="C16" s="38" t="n">
+      <c r="C16" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="38" t="n">
+      <c r="D16" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F16" s="72">
+      <c r="F16" s="73">
         <f>IF(ISNUMBER('Results'!$B$16),'Results'!$B$16*'Results'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="G16" s="72">
+      <c r="G16" s="73">
         <f>IF(ISNUMBER('Results'!$B$16),'Results'!$B$16*'Results'!$D$16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="72">
+      <c r="H16" s="73">
         <f>IF(ISNUMBER('Results'!$B$16),'Results'!$B$16*'Results'!$E$16,0)</f>
         <v/>
       </c>
-      <c r="I16" s="72">
+      <c r="I16" s="73">
         <f>IF(ISNUMBER('Results'!$B$16),15*'Results'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="J16" s="72">
+      <c r="J16" s="73">
         <f>IF(ISNUMBER('Results'!$B$16),15*'Results'!$D$16,0)</f>
         <v/>
       </c>
-      <c r="K16" s="72">
+      <c r="K16" s="73">
         <f>IF(ISNUMBER('Results'!$B$16),15*'Results'!$E$16,0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Carbon processing</t>
         </is>
       </c>
-      <c r="B17" s="72">
+      <c r="B17" s="73">
         <f>IF(COUNT('DEEP Score'!G36:G36)=0,"",SUM('DEEP Score'!G36:G36)/COUNT('DEEP Score'!G36:G36)*15)</f>
         <v/>
       </c>
-      <c r="C17" s="38" t="n">
+      <c r="C17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="38" t="n">
+      <c r="D17" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F17" s="72">
+      <c r="F17" s="73">
         <f>IF(ISNUMBER('Results'!$B$17),'Results'!$B$17*'Results'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="G17" s="72">
+      <c r="G17" s="73">
         <f>IF(ISNUMBER('Results'!$B$17),'Results'!$B$17*'Results'!$D$17,0)</f>
         <v/>
       </c>
-      <c r="H17" s="72">
+      <c r="H17" s="73">
         <f>IF(ISNUMBER('Results'!$B$17),'Results'!$B$17*'Results'!$E$17,0)</f>
         <v/>
       </c>
-      <c r="I17" s="72">
+      <c r="I17" s="73">
         <f>IF(ISNUMBER('Results'!$B$17),15*'Results'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="J17" s="72">
+      <c r="J17" s="73">
         <f>IF(ISNUMBER('Results'!$B$17),15*'Results'!$D$17,0)</f>
         <v/>
       </c>
-      <c r="K17" s="72">
+      <c r="K17" s="73">
         <f>IF(ISNUMBER('Results'!$B$17),15*'Results'!$E$17,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>Habitat provision</t>
         </is>
       </c>
-      <c r="B18" s="72">
+      <c r="B18" s="73">
         <f>IF(COUNT('DEEP Score'!G37:G38)=0,"",SUM('DEEP Score'!G37:G38)/COUNT('DEEP Score'!G37:G38)*15)</f>
         <v/>
       </c>
-      <c r="C18" s="38" t="n">
+      <c r="C18" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="38" t="n">
+      <c r="D18" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="72">
+      <c r="E18" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="73">
         <f>IF(ISNUMBER('Results'!$B$18),'Results'!$B$18*'Results'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="G18" s="72">
+      <c r="G18" s="73">
         <f>IF(ISNUMBER('Results'!$B$18),'Results'!$B$18*'Results'!$D$18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="72">
+      <c r="H18" s="73">
         <f>IF(ISNUMBER('Results'!$B$18),'Results'!$B$18*'Results'!$E$18,0)</f>
         <v/>
       </c>
-      <c r="I18" s="72">
+      <c r="I18" s="73">
         <f>IF(ISNUMBER('Results'!$B$18),15*'Results'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="J18" s="72">
+      <c r="J18" s="73">
         <f>IF(ISNUMBER('Results'!$B$18),15*'Results'!$D$18,0)</f>
         <v/>
       </c>
-      <c r="K18" s="72">
+      <c r="K18" s="73">
         <f>IF(ISNUMBER('Results'!$B$18),15*'Results'!$E$18,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>Watershed connectivity</t>
         </is>
       </c>
-      <c r="B19" s="72">
+      <c r="B19" s="73">
         <f>IF(COUNT('DEEP Score'!G39:G39)=0,"",SUM('DEEP Score'!G39:G39)/COUNT('DEEP Score'!G39:G39)*15)</f>
         <v/>
       </c>
-      <c r="C19" s="38" t="n">
+      <c r="C19" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="D19" s="38" t="n">
+      <c r="D19" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="72">
+      <c r="E19" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="73">
         <f>IF(ISNUMBER('Results'!$B$19),'Results'!$B$19*'Results'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="G19" s="72">
+      <c r="G19" s="73">
         <f>IF(ISNUMBER('Results'!$B$19),'Results'!$B$19*'Results'!$D$19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="72">
+      <c r="H19" s="73">
         <f>IF(ISNUMBER('Results'!$B$19),'Results'!$B$19*'Results'!$E$19,0)</f>
         <v/>
       </c>
-      <c r="I19" s="72">
+      <c r="I19" s="73">
         <f>IF(ISNUMBER('Results'!$B$19),15*'Results'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="J19" s="72">
+      <c r="J19" s="73">
         <f>IF(ISNUMBER('Results'!$B$19),15*'Results'!$D$19,0)</f>
         <v/>
       </c>
-      <c r="K19" s="72">
+      <c r="K19" s="73">
         <f>IF(ISNUMBER('Results'!$B$19),15*'Results'!$E$19,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Sub-index</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>Physical</t>
         </is>
       </c>
-      <c r="B22" s="72">
+      <c r="B22" s="73">
         <f>IF(SUM('Results'!$I$4:$I$19)=0,0,SUM('Results'!$F$4:$F$19)/SUM('Results'!$I$4:$I$19))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>Chemical</t>
         </is>
       </c>
-      <c r="B23" s="72">
+      <c r="B23" s="73">
         <f>IF(SUM('Results'!$J$4:$J$19)=0,0,SUM('Results'!$G$4:$G$19)/SUM('Results'!$J$4:$J$19))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>Biological</t>
         </is>
       </c>
-      <c r="B24" s="72">
+      <c r="B24" s="73">
         <f>IF(SUM('Results'!$K$4:$K$19)=0,0,SUM('Results'!$H$4:$H$19)/SUM('Results'!$K$4:$K$19))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="57" t="inlineStr">
+      <c r="A25" s="58" t="inlineStr">
         <is>
           <t>Ecosystem Condition Index</t>
         </is>
       </c>
-      <c r="B25" s="72">
+      <c r="B25" s="73">
         <f>('Results'!$B$22+'Results'!$B$23+'Results'!$B$24)/3</f>
         <v/>
       </c>
@@ -5863,12 +5938,21 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5883,1690 +5967,1697 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="71" t="inlineStr">
+      <c r="A1" s="72" t="inlineStr">
         <is>
           <t>Reference curves, bands and weights</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>One row per metric and curve set. Knots in ascending x, the last knot repeated to fill eight. The DEEP Score sheet reads these rows.</t>
         </is>
       </c>
     </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Curve key</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Metric id</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Curve set</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Knots</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Scored against</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>x3</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>x4</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>x5</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>x6</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>x7</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>x8</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>y1</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>y2</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>y3</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>y4</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="S4" s="6" t="inlineStr">
         <is>
           <t>y5</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="T4" s="6" t="inlineStr">
         <is>
           <t>y6</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="U4" s="6" t="inlineStr">
         <is>
           <t>y7</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>y8</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>spring_pctag2019ws|</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>spring-pctag2019ws</t>
         </is>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>Agriculture, crop and hay</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr"/>
-      <c r="E5" s="38" t="n">
+      <c r="D5" s="39" t="inlineStr"/>
+      <c r="E5" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="38" t="inlineStr">
+      <c r="F5" s="39" t="inlineStr">
         <is>
           <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
-      <c r="G5" s="38" t="n">
+      <c r="G5" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="38" t="n">
+      <c r="H5" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="I5" s="38" t="n">
+      <c r="I5" s="39" t="n">
         <v>50.005</v>
       </c>
-      <c r="J5" s="38" t="n">
+      <c r="J5" s="39" t="n">
         <v>76.0115</v>
       </c>
-      <c r="K5" s="38" t="n">
+      <c r="K5" s="39" t="n">
         <v>76.0115</v>
       </c>
-      <c r="L5" s="38" t="n">
+      <c r="L5" s="39" t="n">
         <v>76.0115</v>
       </c>
-      <c r="M5" s="38" t="n">
+      <c r="M5" s="39" t="n">
         <v>76.0115</v>
       </c>
-      <c r="N5" s="38" t="n">
+      <c r="N5" s="39" t="n">
         <v>76.0115</v>
       </c>
-      <c r="O5" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="38" t="n">
+      <c r="O5" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="39" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="Q5" s="38" t="n">
+      <c r="Q5" s="39" t="n">
         <v>0.39</v>
       </c>
-      <c r="R5" s="38" t="n">
+      <c r="R5" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="38" t="n">
+      <c r="S5" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="38" t="n">
+      <c r="T5" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="U5" s="38" t="n">
+      <c r="U5" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="38" t="n">
+      <c r="V5" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>spring_pctimp2019ws|</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>spring-pctimp2019ws</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>Impervious surface</t>
         </is>
       </c>
-      <c r="D6" s="38" t="inlineStr"/>
-      <c r="E6" s="38" t="n">
+      <c r="D6" s="39" t="inlineStr"/>
+      <c r="E6" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="38" t="inlineStr">
+      <c r="F6" s="39" t="inlineStr">
         <is>
           <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
-      <c r="G6" s="38" t="n">
+      <c r="G6" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="38" t="n">
+      <c r="H6" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="38" t="n">
+      <c r="I6" s="39" t="n">
         <v>25.005</v>
       </c>
-      <c r="J6" s="38" t="n">
+      <c r="J6" s="39" t="n">
         <v>44.5115</v>
       </c>
-      <c r="K6" s="38" t="n">
+      <c r="K6" s="39" t="n">
         <v>44.5115</v>
       </c>
-      <c r="L6" s="38" t="n">
+      <c r="L6" s="39" t="n">
         <v>44.5115</v>
       </c>
-      <c r="M6" s="38" t="n">
+      <c r="M6" s="39" t="n">
         <v>44.5115</v>
       </c>
-      <c r="N6" s="38" t="n">
+      <c r="N6" s="39" t="n">
         <v>44.5115</v>
       </c>
-      <c r="O6" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="38" t="n">
+      <c r="O6" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="39" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="Q6" s="38" t="n">
+      <c r="Q6" s="39" t="n">
         <v>0.39</v>
       </c>
-      <c r="R6" s="38" t="n">
+      <c r="R6" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="38" t="n">
+      <c r="S6" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="38" t="n">
+      <c r="T6" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="38" t="n">
+      <c r="U6" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="38" t="n">
+      <c r="V6" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>spring_pctwet2019ws|</t>
         </is>
       </c>
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>spring-pctwet2019ws</t>
         </is>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
         <is>
           <t>Wetland</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr"/>
-      <c r="E7" s="38" t="n">
+      <c r="D7" s="39" t="inlineStr"/>
+      <c r="E7" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="38" t="inlineStr">
+      <c r="F7" s="39" t="inlineStr">
         <is>
           <t>10 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G7" s="38" t="n">
+      <c r="G7" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="38" t="n">
+      <c r="H7" s="39" t="n">
         <v>2.878928571428571</v>
       </c>
-      <c r="I7" s="38" t="n">
+      <c r="I7" s="39" t="n">
         <v>6.7175</v>
       </c>
-      <c r="J7" s="38" t="n">
+      <c r="J7" s="39" t="n">
         <v>14.005</v>
       </c>
-      <c r="K7" s="38" t="n">
+      <c r="K7" s="39" t="n">
         <v>16.19125</v>
       </c>
-      <c r="L7" s="38" t="n">
+      <c r="L7" s="39" t="n">
         <v>16.19125</v>
       </c>
-      <c r="M7" s="38" t="n">
+      <c r="M7" s="39" t="n">
         <v>16.19125</v>
       </c>
-      <c r="N7" s="38" t="n">
+      <c r="N7" s="39" t="n">
         <v>16.19125</v>
       </c>
-      <c r="O7" s="38" t="n">
+      <c r="O7" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="38" t="n">
+      <c r="P7" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q7" s="38" t="n">
+      <c r="Q7" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="38" t="n">
+      <c r="R7" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>spring_rddensws|</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>spring-rddensws</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>Road density</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr"/>
-      <c r="E8" s="38" t="n">
+      <c r="D8" s="39" t="inlineStr"/>
+      <c r="E8" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="38" t="inlineStr">
+      <c r="F8" s="39" t="inlineStr">
         <is>
           <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
-      <c r="G8" s="38" t="n">
+      <c r="G8" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="38" t="n">
+      <c r="H8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="38" t="n">
+      <c r="J8" s="39" t="n">
         <v>5.6</v>
       </c>
-      <c r="K8" s="38" t="n">
+      <c r="K8" s="39" t="n">
         <v>5.6</v>
       </c>
-      <c r="L8" s="38" t="n">
+      <c r="L8" s="39" t="n">
         <v>5.6</v>
       </c>
-      <c r="M8" s="38" t="n">
+      <c r="M8" s="39" t="n">
         <v>5.6</v>
       </c>
-      <c r="N8" s="38" t="n">
+      <c r="N8" s="39" t="n">
         <v>5.6</v>
       </c>
-      <c r="O8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="38" t="n">
+      <c r="O8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="39" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="Q8" s="38" t="n">
+      <c r="Q8" s="39" t="n">
         <v>0.39</v>
       </c>
-      <c r="R8" s="38" t="n">
+      <c r="R8" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="38" t="n">
+      <c r="S8" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="38" t="n">
+      <c r="T8" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="38" t="n">
+      <c r="U8" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="38" t="n">
+      <c r="V8" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>spring_bfiws|</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>spring-bfiws</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>Base flow index</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr"/>
-      <c r="E9" s="38" t="n">
+      <c r="D9" s="39" t="inlineStr"/>
+      <c r="E9" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="38" t="inlineStr">
+      <c r="F9" s="39" t="inlineStr">
         <is>
           <t>10 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G9" s="38" t="n">
+      <c r="G9" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="38" t="n">
+      <c r="H9" s="39" t="n">
         <v>21.53571428571428</v>
       </c>
-      <c r="I9" s="38" t="n">
+      <c r="I9" s="39" t="n">
         <v>50.25</v>
       </c>
-      <c r="J9" s="38" t="n">
+      <c r="J9" s="39" t="n">
         <v>54.51965</v>
       </c>
-      <c r="K9" s="38" t="n">
+      <c r="K9" s="39" t="n">
         <v>55.800545</v>
       </c>
-      <c r="L9" s="38" t="n">
+      <c r="L9" s="39" t="n">
         <v>55.800545</v>
       </c>
-      <c r="M9" s="38" t="n">
+      <c r="M9" s="39" t="n">
         <v>55.800545</v>
       </c>
-      <c r="N9" s="38" t="n">
+      <c r="N9" s="39" t="n">
         <v>55.800545</v>
       </c>
-      <c r="O9" s="38" t="n">
+      <c r="O9" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="38" t="n">
+      <c r="P9" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q9" s="38" t="n">
+      <c r="Q9" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="38" t="n">
+      <c r="R9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>spring_dorws|</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>spring-dorws</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
         <is>
           <t>Degree of regulation</t>
         </is>
       </c>
-      <c r="D10" s="38" t="inlineStr"/>
-      <c r="E10" s="38" t="n">
+      <c r="D10" s="39" t="inlineStr"/>
+      <c r="E10" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="38" t="inlineStr">
+      <c r="F10" s="39" t="inlineStr">
         <is>
           <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
-      <c r="G10" s="38" t="n">
+      <c r="G10" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="38" t="n">
+      <c r="H10" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="38" t="n">
+      <c r="I10" s="39" t="n">
         <v>15.005</v>
       </c>
-      <c r="J10" s="38" t="n">
+      <c r="J10" s="39" t="n">
         <v>31.9115</v>
       </c>
-      <c r="K10" s="38" t="n">
+      <c r="K10" s="39" t="n">
         <v>31.9115</v>
       </c>
-      <c r="L10" s="38" t="n">
+      <c r="L10" s="39" t="n">
         <v>31.9115</v>
       </c>
-      <c r="M10" s="38" t="n">
+      <c r="M10" s="39" t="n">
         <v>31.9115</v>
       </c>
-      <c r="N10" s="38" t="n">
+      <c r="N10" s="39" t="n">
         <v>31.9115</v>
       </c>
-      <c r="O10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="38" t="n">
+      <c r="O10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="39" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="Q10" s="38" t="n">
+      <c r="Q10" s="39" t="n">
         <v>0.39</v>
       </c>
-      <c r="R10" s="38" t="n">
+      <c r="R10" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="38" t="n">
+      <c r="S10" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="38" t="n">
+      <c r="T10" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="U10" s="38" t="n">
+      <c r="U10" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="38" t="n">
+      <c r="V10" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>spring_phab_bfwd_rat|</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>spring-phab-bfwd-rat</t>
         </is>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>Bankfull width:depth ratio</t>
         </is>
       </c>
-      <c r="D11" s="38" t="inlineStr"/>
-      <c r="E11" s="38" t="n">
+      <c r="D11" s="39" t="inlineStr"/>
+      <c r="E11" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="F11" s="38" t="inlineStr">
+      <c r="F11" s="39" t="inlineStr">
         <is>
           <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G11" s="38" t="n">
+      <c r="G11" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="38" t="n">
+      <c r="H11" s="39" t="n">
         <v>3.66112859249115</v>
       </c>
-      <c r="I11" s="38" t="n">
+      <c r="I11" s="39" t="n">
         <v>7.60732889175415</v>
       </c>
-      <c r="J11" s="38" t="n">
+      <c r="J11" s="39" t="n">
         <v>18.88218688964844</v>
       </c>
-      <c r="K11" s="38" t="n">
+      <c r="K11" s="39" t="n">
         <v>22.82838718891144</v>
       </c>
-      <c r="L11" s="38" t="n">
+      <c r="L11" s="39" t="n">
         <v>30.15704488754272</v>
       </c>
-      <c r="M11" s="38" t="n">
+      <c r="M11" s="39" t="n">
         <v>41.43190288543701</v>
       </c>
-      <c r="N11" s="38" t="n">
+      <c r="N11" s="39" t="n">
         <v>41.43190288543701</v>
       </c>
-      <c r="O11" s="38" t="n">
+      <c r="O11" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="38" t="n">
+      <c r="P11" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" s="38" t="n">
+      <c r="Q11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="T11" s="38" t="n">
+      <c r="T11" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="U11" s="38" t="n">
+      <c r="U11" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="38" t="n">
+      <c r="V11" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>spring_phab_rp100_cm|</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>spring-phab-rp100-cm</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>Residual pool depth</t>
         </is>
       </c>
-      <c r="D12" s="38" t="inlineStr"/>
-      <c r="E12" s="38" t="n">
+      <c r="D12" s="39" t="inlineStr"/>
+      <c r="E12" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="38" t="inlineStr">
+      <c r="F12" s="39" t="inlineStr">
         <is>
           <t>12 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G12" s="38" t="n">
+      <c r="G12" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="38" t="n">
+      <c r="H12" s="39" t="n">
         <v>4.66008905002049</v>
       </c>
-      <c r="I12" s="38" t="n">
+      <c r="I12" s="39" t="n">
         <v>10.87354111671448</v>
       </c>
-      <c r="J12" s="38" t="n">
+      <c r="J12" s="39" t="n">
         <v>29.8195538520813</v>
       </c>
-      <c r="K12" s="38" t="n">
+      <c r="K12" s="39" t="n">
         <v>35.50335767269134</v>
       </c>
-      <c r="L12" s="38" t="n">
+      <c r="L12" s="39" t="n">
         <v>35.50335767269134</v>
       </c>
-      <c r="M12" s="38" t="n">
+      <c r="M12" s="39" t="n">
         <v>35.50335767269134</v>
       </c>
-      <c r="N12" s="38" t="n">
+      <c r="N12" s="39" t="n">
         <v>35.50335767269134</v>
       </c>
-      <c r="O12" s="38" t="n">
+      <c r="O12" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="38" t="n">
+      <c r="P12" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q12" s="38" t="n">
+      <c r="Q12" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R12" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="38" t="n">
+      <c r="R12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>spring_phab_xbkf_h|</t>
         </is>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>spring-phab-xbkf-h</t>
         </is>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="39" t="inlineStr">
         <is>
           <t>Bankfull height above channel</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr"/>
-      <c r="E13" s="38" t="n">
+      <c r="D13" s="39" t="inlineStr"/>
+      <c r="E13" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="38" t="inlineStr">
+      <c r="F13" s="39" t="inlineStr">
         <is>
           <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G13" s="38" t="n">
+      <c r="G13" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="38" t="n">
+      <c r="H13" s="39" t="n">
         <v>0.0663636326789856</v>
       </c>
-      <c r="I13" s="38" t="n">
+      <c r="I13" s="39" t="n">
         <v>0.3363636434078217</v>
       </c>
-      <c r="J13" s="38" t="n">
+      <c r="J13" s="39" t="n">
         <v>0.4308636471629143</v>
       </c>
-      <c r="K13" s="38" t="n">
+      <c r="K13" s="39" t="n">
         <v>0.6063636541366577</v>
       </c>
-      <c r="L13" s="38" t="n">
+      <c r="L13" s="39" t="n">
         <v>0.8763636648654938</v>
       </c>
-      <c r="M13" s="38" t="n">
+      <c r="M13" s="39" t="n">
         <v>0.8763636648654938</v>
       </c>
-      <c r="N13" s="38" t="n">
+      <c r="N13" s="39" t="n">
         <v>0.8763636648654938</v>
       </c>
-      <c r="O13" s="38" t="n">
+      <c r="O13" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" s="38" t="n">
+      <c r="P13" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="S13" s="38" t="n">
+      <c r="S13" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="T13" s="38" t="n">
+      <c r="T13" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="U13" s="38" t="n">
+      <c r="U13" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="38" t="n">
+      <c r="V13" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>spring_phab_pct_safn|</t>
         </is>
       </c>
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>spring-phab-pct-safn</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <t>Sand + fines</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr"/>
-      <c r="E14" s="38" t="n">
+      <c r="D14" s="39" t="inlineStr"/>
+      <c r="E14" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="38" t="inlineStr">
+      <c r="F14" s="39" t="inlineStr">
         <is>
           <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
         </is>
       </c>
-      <c r="G14" s="38" t="n">
+      <c r="G14" s="39" t="n">
         <v>8.833333396911623</v>
       </c>
-      <c r="H14" s="38" t="n">
+      <c r="H14" s="39" t="n">
         <v>28.33333396911621</v>
       </c>
-      <c r="I14" s="38" t="n">
+      <c r="I14" s="39" t="n">
         <v>93.33333587646484</v>
       </c>
-      <c r="J14" s="38" t="n">
+      <c r="J14" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="K14" s="38" t="n">
+      <c r="K14" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="L14" s="38" t="n">
+      <c r="L14" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="M14" s="38" t="n">
+      <c r="M14" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="N14" s="38" t="n">
+      <c r="N14" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="O14" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="38" t="n">
+      <c r="O14" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R14" s="38" t="n">
+      <c r="R14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="38" t="n">
+      <c r="S14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="T14" s="38" t="n">
+      <c r="T14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="U14" s="38" t="n">
+      <c r="U14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="38" t="n">
+      <c r="V14" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>spring_phab_xembed|</t>
         </is>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>spring-phab-xembed</t>
         </is>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C15" s="39" t="inlineStr">
         <is>
           <t>Embeddedness</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr"/>
-      <c r="E15" s="38" t="n">
+      <c r="D15" s="39" t="inlineStr"/>
+      <c r="E15" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="38" t="inlineStr">
+      <c r="F15" s="39" t="inlineStr">
         <is>
           <t>12 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
         </is>
       </c>
-      <c r="G15" s="38" t="n">
+      <c r="G15" s="39" t="n">
         <v>21.04727163314819</v>
       </c>
-      <c r="H15" s="38" t="n">
+      <c r="H15" s="39" t="n">
         <v>33.70454502105713</v>
       </c>
-      <c r="I15" s="38" t="n">
+      <c r="I15" s="39" t="n">
         <v>75.89545631408691</v>
       </c>
-      <c r="J15" s="38" t="n">
+      <c r="J15" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="K15" s="38" t="n">
+      <c r="K15" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="L15" s="38" t="n">
+      <c r="L15" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="M15" s="38" t="n">
+      <c r="M15" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="N15" s="38" t="n">
+      <c r="N15" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="O15" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="38" t="n">
+      <c r="O15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R15" s="38" t="n">
+      <c r="R15" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="38" t="n">
+      <c r="S15" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="T15" s="38" t="n">
+      <c r="T15" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="U15" s="38" t="n">
+      <c r="U15" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="38" t="n">
+      <c r="V15" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>spring_phab_sinu|</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>spring-phab-sinu</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="39" t="inlineStr">
         <is>
           <t>Sinuosity</t>
         </is>
       </c>
-      <c r="D16" s="38" t="inlineStr"/>
-      <c r="E16" s="38" t="n">
+      <c r="D16" s="39" t="inlineStr"/>
+      <c r="E16" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="38" t="inlineStr">
+      <c r="F16" s="39" t="inlineStr">
         <is>
           <t>12 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="38" t="n">
+      <c r="G16" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="39" t="n">
         <v>1.141691654920578</v>
       </c>
-      <c r="I16" s="38" t="n">
+      <c r="I16" s="39" t="n">
         <v>1.515197157859802</v>
       </c>
-      <c r="J16" s="38" t="n">
+      <c r="J16" s="39" t="n">
         <v>1.62724880874157</v>
       </c>
-      <c r="K16" s="38" t="n">
+      <c r="K16" s="39" t="n">
         <v>1.62724880874157</v>
       </c>
-      <c r="L16" s="38" t="n">
+      <c r="L16" s="39" t="n">
         <v>1.62724880874157</v>
       </c>
-      <c r="M16" s="38" t="n">
+      <c r="M16" s="39" t="n">
         <v>1.62724880874157</v>
       </c>
-      <c r="N16" s="38" t="n">
+      <c r="N16" s="39" t="n">
         <v>1.62724880874157</v>
       </c>
-      <c r="O16" s="38" t="n">
+      <c r="O16" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="38" t="n">
+      <c r="P16" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="38" t="n">
+      <c r="Q16" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>spring_phab_xbka|</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>spring-phab-xbka</t>
         </is>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="39" t="inlineStr">
         <is>
           <t>Bank angle</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr"/>
-      <c r="E17" s="38" t="n">
+      <c r="D17" s="39" t="inlineStr"/>
+      <c r="E17" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="38" t="inlineStr">
+      <c r="F17" s="39" t="inlineStr">
         <is>
           <t>12 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
         </is>
       </c>
-      <c r="G17" s="38" t="n">
+      <c r="G17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="38" t="n">
+      <c r="H17" s="39" t="n">
         <v>15.10568132400513</v>
       </c>
-      <c r="I17" s="38" t="n">
+      <c r="I17" s="39" t="n">
         <v>23.70454502105713</v>
       </c>
-      <c r="J17" s="38" t="n">
+      <c r="J17" s="39" t="n">
         <v>48.27272701263428</v>
       </c>
-      <c r="K17" s="38" t="n">
+      <c r="K17" s="39" t="n">
         <v>56.87159070968628</v>
       </c>
-      <c r="L17" s="38" t="n">
+      <c r="L17" s="39" t="n">
         <v>72.84090900421143</v>
       </c>
-      <c r="M17" s="38" t="n">
+      <c r="M17" s="39" t="n">
         <v>97.40909099578857</v>
       </c>
-      <c r="N17" s="38" t="n">
+      <c r="N17" s="39" t="n">
         <v>97.40909099578857</v>
       </c>
-      <c r="O17" s="38" t="n">
+      <c r="O17" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="P17" s="38" t="n">
+      <c r="P17" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q17" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" s="38" t="n">
+      <c r="Q17" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="T17" s="38" t="n">
+      <c r="T17" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="U17" s="38" t="n">
+      <c r="U17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="38" t="n">
+      <c r="V17" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>spring_phab_lrbs_use|</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>spring-phab-lrbs-use</t>
         </is>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>Relative bed stability</t>
         </is>
       </c>
-      <c r="D18" s="38" t="inlineStr"/>
-      <c r="E18" s="38" t="n">
+      <c r="D18" s="39" t="inlineStr"/>
+      <c r="E18" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="F18" s="38" t="inlineStr">
+      <c r="F18" s="39" t="inlineStr">
         <is>
           <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G18" s="38" t="n">
+      <c r="G18" s="39" t="n">
         <v>-8.386457562446594</v>
       </c>
-      <c r="H18" s="38" t="n">
+      <c r="H18" s="39" t="n">
         <v>-5.447064220905304</v>
       </c>
-      <c r="I18" s="38" t="n">
+      <c r="I18" s="39" t="n">
         <v>-3.536458548903465</v>
       </c>
-      <c r="J18" s="38" t="n">
+      <c r="J18" s="39" t="n">
         <v>-2.507670879364014</v>
       </c>
-      <c r="K18" s="38" t="n">
+      <c r="K18" s="39" t="n">
         <v>0.4317224621772766</v>
       </c>
-      <c r="L18" s="38" t="n">
+      <c r="L18" s="39" t="n">
         <v>1.460510131716728</v>
       </c>
-      <c r="M18" s="38" t="n">
+      <c r="M18" s="39" t="n">
         <v>3.371115803718567</v>
       </c>
-      <c r="N18" s="38" t="n">
+      <c r="N18" s="39" t="n">
         <v>6.310509145259857</v>
       </c>
-      <c r="O18" s="38" t="n">
+      <c r="O18" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="38" t="n">
+      <c r="P18" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q18" s="38" t="n">
+      <c r="Q18" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" s="38" t="n">
+      <c r="R18" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" s="38" t="n">
+      <c r="U18" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="V18" s="38" t="n">
+      <c r="V18" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>spring_phab_lsub_dmm|</t>
         </is>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>spring-phab-lsub-dmm</t>
         </is>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C19" s="39" t="inlineStr">
         <is>
           <t>Substrate size</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr"/>
-      <c r="E19" s="38" t="n">
+      <c r="D19" s="39" t="inlineStr"/>
+      <c r="E19" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="38" t="inlineStr">
+      <c r="F19" s="39" t="inlineStr">
         <is>
           <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
         </is>
       </c>
-      <c r="G19" s="38" t="n">
+      <c r="G19" s="39" t="n">
         <v>-9.235586563746136</v>
       </c>
-      <c r="H19" s="38" t="n">
+      <c r="H19" s="39" t="n">
         <v>-6.072640101114909</v>
       </c>
-      <c r="I19" s="38" t="n">
+      <c r="I19" s="39" t="n">
         <v>-1.855378150939941</v>
       </c>
-      <c r="J19" s="38" t="n">
+      <c r="J19" s="39" t="n">
         <v>1.307568311691284</v>
       </c>
-      <c r="K19" s="38" t="n">
+      <c r="K19" s="39" t="n">
         <v>2.256452250480652</v>
       </c>
-      <c r="L19" s="38" t="n">
+      <c r="L19" s="39" t="n">
         <v>2.256452250480652</v>
       </c>
-      <c r="M19" s="38" t="n">
+      <c r="M19" s="39" t="n">
         <v>2.256452250480652</v>
       </c>
-      <c r="N19" s="38" t="n">
+      <c r="N19" s="39" t="n">
         <v>2.256452250480652</v>
       </c>
-      <c r="O19" s="38" t="n">
+      <c r="O19" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="38" t="n">
+      <c r="P19" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q19" s="38" t="n">
+      <c r="Q19" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R19" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="38" t="n">
+      <c r="R19" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>spring_phab_lwdeqvolm100|</t>
         </is>
       </c>
-      <c r="B20" s="38" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>spring-phab-lwdeqvolm100</t>
         </is>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C20" s="39" t="inlineStr">
         <is>
           <t>Large wood volume</t>
         </is>
       </c>
-      <c r="D20" s="38" t="inlineStr"/>
-      <c r="E20" s="38" t="n">
+      <c r="D20" s="39" t="inlineStr"/>
+      <c r="E20" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="F20" s="38" t="inlineStr">
+      <c r="F20" s="39" t="inlineStr">
         <is>
           <t>14 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G20" s="38" t="n">
+      <c r="G20" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="38" t="n">
+      <c r="H20" s="39" t="n">
         <v>0.06622835461582456</v>
       </c>
-      <c r="I20" s="38" t="n">
+      <c r="I20" s="39" t="n">
         <v>0.154532827436924</v>
       </c>
-      <c r="J20" s="38" t="n">
+      <c r="J20" s="39" t="n">
         <v>3.242602586746216</v>
       </c>
-      <c r="K20" s="38" t="n">
+      <c r="K20" s="39" t="n">
         <v>4.169023514539004</v>
       </c>
-      <c r="L20" s="38" t="n">
+      <c r="L20" s="39" t="n">
         <v>4.169023514539004</v>
       </c>
-      <c r="M20" s="38" t="n">
+      <c r="M20" s="39" t="n">
         <v>4.169023514539004</v>
       </c>
-      <c r="N20" s="38" t="n">
+      <c r="N20" s="39" t="n">
         <v>4.169023514539004</v>
       </c>
-      <c r="O20" s="38" t="n">
+      <c r="O20" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="38" t="n">
+      <c r="P20" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q20" s="38" t="n">
+      <c r="Q20" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R20" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="38" t="n">
+      <c r="R20" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>spring_phab_xcdenmid|</t>
         </is>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>spring-phab-xcdenmid</t>
         </is>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="39" t="inlineStr">
         <is>
           <t>Canopy density, mid-channel</t>
         </is>
       </c>
-      <c r="D21" s="38" t="inlineStr"/>
-      <c r="E21" s="38" t="n">
+      <c r="D21" s="39" t="inlineStr"/>
+      <c r="E21" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="38" t="inlineStr">
+      <c r="F21" s="39" t="inlineStr">
         <is>
           <t>12 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G21" s="38" t="n">
+      <c r="G21" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="38" t="n">
+      <c r="H21" s="39" t="n">
         <v>10.85752507618495</v>
       </c>
-      <c r="I21" s="38" t="n">
+      <c r="I21" s="39" t="n">
         <v>25.33422517776489</v>
       </c>
-      <c r="J21" s="38" t="n">
+      <c r="J21" s="39" t="n">
         <v>91.97860717773438</v>
       </c>
-      <c r="K21" s="38" t="n">
+      <c r="K21" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="L21" s="38" t="n">
+      <c r="L21" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="M21" s="38" t="n">
+      <c r="M21" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="N21" s="38" t="n">
+      <c r="N21" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="O21" s="38" t="n">
+      <c r="O21" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="38" t="n">
+      <c r="P21" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q21" s="38" t="n">
+      <c r="Q21" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R21" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="38" t="n">
+      <c r="R21" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>spring_phab_xcmgw|</t>
         </is>
       </c>
-      <c r="B22" s="38" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>spring-phab-xcmgw</t>
         </is>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C22" s="39" t="inlineStr">
         <is>
           <t>Riparian veg cover, woody</t>
         </is>
       </c>
-      <c r="D22" s="38" t="inlineStr"/>
-      <c r="E22" s="38" t="n">
+      <c r="D22" s="39" t="inlineStr"/>
+      <c r="E22" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="38" t="inlineStr">
+      <c r="F22" s="39" t="inlineStr">
         <is>
           <t>14 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G22" s="38" t="n">
+      <c r="G22" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="38" t="n">
+      <c r="H22" s="39" t="n">
         <v>0.3031655890601022</v>
       </c>
-      <c r="I22" s="38" t="n">
+      <c r="I22" s="39" t="n">
         <v>0.7073863744735718</v>
       </c>
-      <c r="J22" s="38" t="n">
+      <c r="J22" s="39" t="n">
         <v>1.530499160289764</v>
       </c>
-      <c r="K22" s="38" t="n">
+      <c r="K22" s="39" t="n">
         <v>1.777432996034622</v>
       </c>
-      <c r="L22" s="38" t="n">
+      <c r="L22" s="39" t="n">
         <v>1.777432996034622</v>
       </c>
-      <c r="M22" s="38" t="n">
+      <c r="M22" s="39" t="n">
         <v>1.777432996034622</v>
       </c>
-      <c r="N22" s="38" t="n">
+      <c r="N22" s="39" t="n">
         <v>1.777432996034622</v>
       </c>
-      <c r="O22" s="38" t="n">
+      <c r="O22" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="38" t="n">
+      <c r="P22" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q22" s="38" t="n">
+      <c r="Q22" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R22" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="38" t="n">
+      <c r="R22" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>spring_phab_pct_fast|</t>
         </is>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
         <is>
           <t>spring-phab-pct-fast</t>
         </is>
       </c>
-      <c r="C23" s="38" t="inlineStr">
+      <c r="C23" s="39" t="inlineStr">
         <is>
           <t>Fast-water / riffle habitat</t>
         </is>
       </c>
-      <c r="D23" s="38" t="inlineStr"/>
-      <c r="E23" s="38" t="n">
+      <c r="D23" s="39" t="inlineStr"/>
+      <c r="E23" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="38" t="inlineStr"/>
-      <c r="G23" s="38" t="n">
+      <c r="F23" s="39" t="inlineStr"/>
+      <c r="G23" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="38" t="n">
+      <c r="H23" s="39" t="n">
         <v>26</v>
       </c>
-      <c r="I23" s="38" t="n">
+      <c r="I23" s="39" t="n">
         <v>26</v>
       </c>
-      <c r="J23" s="38" t="n">
+      <c r="J23" s="39" t="n">
         <v>26</v>
       </c>
-      <c r="K23" s="38" t="n">
+      <c r="K23" s="39" t="n">
         <v>26</v>
       </c>
-      <c r="L23" s="38" t="n">
+      <c r="L23" s="39" t="n">
         <v>26</v>
       </c>
-      <c r="M23" s="38" t="n">
+      <c r="M23" s="39" t="n">
         <v>26</v>
       </c>
-      <c r="N23" s="38" t="n">
+      <c r="N23" s="39" t="n">
         <v>26</v>
       </c>
-      <c r="O23" s="38" t="n">
+      <c r="O23" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P23" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="38" t="n">
+      <c r="P23" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>spring_phab_xfc_nat|</t>
         </is>
       </c>
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>spring-phab-xfc-nat</t>
         </is>
       </c>
-      <c r="C24" s="38" t="inlineStr">
+      <c r="C24" s="39" t="inlineStr">
         <is>
           <t>Natural fish cover</t>
         </is>
       </c>
-      <c r="D24" s="38" t="inlineStr"/>
-      <c r="E24" s="38" t="n">
+      <c r="D24" s="39" t="inlineStr"/>
+      <c r="E24" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="38" t="inlineStr">
+      <c r="F24" s="39" t="inlineStr">
         <is>
           <t>14 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
         </is>
       </c>
-      <c r="G24" s="38" t="n">
+      <c r="G24" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="38" t="n">
+      <c r="H24" s="39" t="n">
         <v>0.0609740245022944</v>
       </c>
-      <c r="I24" s="38" t="n">
+      <c r="I24" s="39" t="n">
         <v>0.1422727238386869</v>
       </c>
-      <c r="J24" s="38" t="n">
+      <c r="J24" s="39" t="n">
         <v>0.6181818097829819</v>
       </c>
-      <c r="K24" s="38" t="n">
+      <c r="K24" s="39" t="n">
         <v>0.7609545355662704</v>
       </c>
-      <c r="L24" s="38" t="n">
+      <c r="L24" s="39" t="n">
         <v>0.7609545355662704</v>
       </c>
-      <c r="M24" s="38" t="n">
+      <c r="M24" s="39" t="n">
         <v>0.7609545355662704</v>
       </c>
-      <c r="N24" s="38" t="n">
+      <c r="N24" s="39" t="n">
         <v>0.7609545355662704</v>
       </c>
-      <c r="O24" s="38" t="n">
+      <c r="O24" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="P24" s="38" t="n">
+      <c r="P24" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="38" t="n">
+      <c r="Q24" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="R24" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="38" t="n">
+      <c r="R24" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="inlineStr">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>spring_nid_dams_1mi|</t>
         </is>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>spring-nid-dams-1mi</t>
         </is>
       </c>
-      <c r="C25" s="38" t="inlineStr">
+      <c r="C25" s="39" t="inlineStr">
         <is>
           <t>Mapped dams within one mile</t>
         </is>
       </c>
-      <c r="D25" s="38" t="inlineStr"/>
-      <c r="E25" s="38" t="n">
+      <c r="D25" s="39" t="inlineStr"/>
+      <c r="E25" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="38" t="inlineStr">
+      <c r="F25" s="39" t="inlineStr">
         <is>
           <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
-      <c r="G25" s="38" t="n">
+      <c r="G25" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="38" t="n">
+      <c r="H25" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="38" t="n">
+      <c r="J25" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="K25" s="38" t="n">
+      <c r="K25" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="L25" s="38" t="n">
+      <c r="L25" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="M25" s="38" t="n">
+      <c r="M25" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="N25" s="38" t="n">
+      <c r="N25" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="O25" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="38" t="n">
+      <c r="O25" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="39" t="n">
         <v>0.545</v>
       </c>
-      <c r="Q25" s="38" t="n">
+      <c r="Q25" s="39" t="n">
         <v>0.195</v>
       </c>
-      <c r="R25" s="38" t="n">
+      <c r="R25" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="38" t="n">
+      <c r="S25" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="38" t="n">
+      <c r="T25" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="U25" s="38" t="n">
+      <c r="U25" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="38" t="n">
+      <c r="V25" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="61" t="inlineStr">
+      <c r="A28" s="62" t="inlineStr">
         <is>
           <t>Curve sets by metric</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="61" t="inlineStr">
+      <c r="A31" s="62" t="inlineStr">
         <is>
           <t>Condition classes</t>
         </is>
@@ -7595,13 +7686,25 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
+  <mergeCells count="1">
+    <mergeCell ref="A3:D3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7613,201 +7716,212 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="71" t="inlineStr">
+      <c r="A1" s="72" t="inlineStr">
         <is>
           <t>Metadata and version information</t>
         </is>
       </c>
     </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Assessment id</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>eastern-corn-belt-plains</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>Assessment name</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Eastern Corn Belt Plains reference assessment</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n">
+      <c r="B6" s="39" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>Lifecycle status</t>
         </is>
       </c>
-      <c r="B7" s="38" t="inlineStr"/>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>Preliminary</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>Content digest</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>sha256:bc2948a42062bb90030672afe31eb3271f563c790dee145c5cb8d7af8dfa42fd</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>ecoregion 55 Eastern Corn Belt Plains</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>StreamCurves reference-curve development</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>Reference method</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>pressure-screen</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Reference screen</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>least-disturbed-v1 (strict), wadeable non-canal frame</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>Scoring method</t>
         </is>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>iqr-seed-v2</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>Functions scored</t>
         </is>
       </c>
-      <c r="B14" s="38" t="n">
+      <c r="B14" s="39" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>Metrics</t>
         </is>
       </c>
-      <c r="B15" s="38" t="n">
+      <c r="B15" s="39" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Function coverage</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>This assessment covers 16 of 20 STAF functions (4 documented exclusions).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Generator</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>streamcurves.deep_calculator</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>Generator version</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr">
-        <is>
-          <t>1.0</t>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>1.1</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>Formula vocabulary</t>
         </is>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>IF AND MIN MAX INDEX MATCH IFERROR ISNUMBER COUNT SUM NA</t>
         </is>
@@ -7815,13 +7929,25 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7832,34 +7958,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Chart series (hidden). One column per class so each bar takes the class colour.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="B2" s="62" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="62" t="inlineStr">
         <is>
           <t>Non-Functioning (0-5)</t>
         </is>
       </c>
-      <c r="D2" s="61" t="inlineStr">
+      <c r="D2" s="62" t="inlineStr">
         <is>
           <t>Functioning At-Risk (6-10)</t>
         </is>
       </c>
-      <c r="E2" s="61" t="inlineStr">
+      <c r="E2" s="62" t="inlineStr">
         <is>
           <t>Functioning (11-15)</t>
         </is>
@@ -7875,15 +8001,15 @@
         <f>IF('Results'!$B$4="","",'Results'!$B$4)</f>
         <v/>
       </c>
-      <c r="C3" s="74">
+      <c r="C3" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$3),IF('ChartData'!$B$3&lt;=5,'ChartData'!$B$3,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D3" s="74">
+      <c r="D3" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$3),IF(AND('ChartData'!$B$3&gt;5,'ChartData'!$B$3&lt;=10),'ChartData'!$B$3,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E3" s="74">
+      <c r="E3" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$3),IF('ChartData'!$B$3&gt;10,'ChartData'!$B$3,NA()),NA())</f>
         <v/>
       </c>
@@ -7898,15 +8024,15 @@
         <f>IF('Results'!$B$5="","",'Results'!$B$5)</f>
         <v/>
       </c>
-      <c r="C4" s="74">
+      <c r="C4" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$4),IF('ChartData'!$B$4&lt;=5,'ChartData'!$B$4,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D4" s="74">
+      <c r="D4" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$4),IF(AND('ChartData'!$B$4&gt;5,'ChartData'!$B$4&lt;=10),'ChartData'!$B$4,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E4" s="74">
+      <c r="E4" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$4),IF('ChartData'!$B$4&gt;10,'ChartData'!$B$4,NA()),NA())</f>
         <v/>
       </c>
@@ -7921,15 +8047,15 @@
         <f>IF('Results'!$B$6="","",'Results'!$B$6)</f>
         <v/>
       </c>
-      <c r="C5" s="74">
+      <c r="C5" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$5),IF('ChartData'!$B$5&lt;=5,'ChartData'!$B$5,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D5" s="74">
+      <c r="D5" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$5),IF(AND('ChartData'!$B$5&gt;5,'ChartData'!$B$5&lt;=10),'ChartData'!$B$5,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E5" s="74">
+      <c r="E5" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$5),IF('ChartData'!$B$5&gt;10,'ChartData'!$B$5,NA()),NA())</f>
         <v/>
       </c>
@@ -7944,15 +8070,15 @@
         <f>IF('Results'!$B$7="","",'Results'!$B$7)</f>
         <v/>
       </c>
-      <c r="C6" s="74">
+      <c r="C6" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$6),IF('ChartData'!$B$6&lt;=5,'ChartData'!$B$6,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$6),IF(AND('ChartData'!$B$6&gt;5,'ChartData'!$B$6&lt;=10),'ChartData'!$B$6,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E6" s="74">
+      <c r="E6" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$6),IF('ChartData'!$B$6&gt;10,'ChartData'!$B$6,NA()),NA())</f>
         <v/>
       </c>
@@ -7967,15 +8093,15 @@
         <f>IF('Results'!$B$8="","",'Results'!$B$8)</f>
         <v/>
       </c>
-      <c r="C7" s="74">
+      <c r="C7" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$7),IF('ChartData'!$B$7&lt;=5,'ChartData'!$B$7,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D7" s="74">
+      <c r="D7" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$7),IF(AND('ChartData'!$B$7&gt;5,'ChartData'!$B$7&lt;=10),'ChartData'!$B$7,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E7" s="74">
+      <c r="E7" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$7),IF('ChartData'!$B$7&gt;10,'ChartData'!$B$7,NA()),NA())</f>
         <v/>
       </c>
@@ -7990,15 +8116,15 @@
         <f>IF('Results'!$B$9="","",'Results'!$B$9)</f>
         <v/>
       </c>
-      <c r="C8" s="74">
+      <c r="C8" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$8),IF('ChartData'!$B$8&lt;=5,'ChartData'!$B$8,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$8),IF(AND('ChartData'!$B$8&gt;5,'ChartData'!$B$8&lt;=10),'ChartData'!$B$8,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E8" s="74">
+      <c r="E8" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$8),IF('ChartData'!$B$8&gt;10,'ChartData'!$B$8,NA()),NA())</f>
         <v/>
       </c>
@@ -8013,15 +8139,15 @@
         <f>IF('Results'!$B$10="","",'Results'!$B$10)</f>
         <v/>
       </c>
-      <c r="C9" s="74">
+      <c r="C9" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$9),IF('ChartData'!$B$9&lt;=5,'ChartData'!$B$9,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D9" s="74">
+      <c r="D9" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$9),IF(AND('ChartData'!$B$9&gt;5,'ChartData'!$B$9&lt;=10),'ChartData'!$B$9,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E9" s="74">
+      <c r="E9" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$9),IF('ChartData'!$B$9&gt;10,'ChartData'!$B$9,NA()),NA())</f>
         <v/>
       </c>
@@ -8036,15 +8162,15 @@
         <f>IF('Results'!$B$11="","",'Results'!$B$11)</f>
         <v/>
       </c>
-      <c r="C10" s="74">
+      <c r="C10" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$10),IF('ChartData'!$B$10&lt;=5,'ChartData'!$B$10,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$10),IF(AND('ChartData'!$B$10&gt;5,'ChartData'!$B$10&lt;=10),'ChartData'!$B$10,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E10" s="74">
+      <c r="E10" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$10),IF('ChartData'!$B$10&gt;10,'ChartData'!$B$10,NA()),NA())</f>
         <v/>
       </c>
@@ -8059,15 +8185,15 @@
         <f>IF('Results'!$B$12="","",'Results'!$B$12)</f>
         <v/>
       </c>
-      <c r="C11" s="74">
+      <c r="C11" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$11),IF('ChartData'!$B$11&lt;=5,'ChartData'!$B$11,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$11),IF(AND('ChartData'!$B$11&gt;5,'ChartData'!$B$11&lt;=10),'ChartData'!$B$11,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E11" s="74">
+      <c r="E11" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$11),IF('ChartData'!$B$11&gt;10,'ChartData'!$B$11,NA()),NA())</f>
         <v/>
       </c>
@@ -8082,15 +8208,15 @@
         <f>IF('Results'!$B$13="","",'Results'!$B$13)</f>
         <v/>
       </c>
-      <c r="C12" s="74">
+      <c r="C12" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$12),IF('ChartData'!$B$12&lt;=5,'ChartData'!$B$12,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$12),IF(AND('ChartData'!$B$12&gt;5,'ChartData'!$B$12&lt;=10),'ChartData'!$B$12,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$12),IF('ChartData'!$B$12&gt;10,'ChartData'!$B$12,NA()),NA())</f>
         <v/>
       </c>
@@ -8105,15 +8231,15 @@
         <f>IF('Results'!$B$14="","",'Results'!$B$14)</f>
         <v/>
       </c>
-      <c r="C13" s="74">
+      <c r="C13" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$13),IF('ChartData'!$B$13&lt;=5,'ChartData'!$B$13,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D13" s="74">
+      <c r="D13" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$13),IF(AND('ChartData'!$B$13&gt;5,'ChartData'!$B$13&lt;=10),'ChartData'!$B$13,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E13" s="74">
+      <c r="E13" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$13),IF('ChartData'!$B$13&gt;10,'ChartData'!$B$13,NA()),NA())</f>
         <v/>
       </c>
@@ -8128,15 +8254,15 @@
         <f>IF('Results'!$B$15="","",'Results'!$B$15)</f>
         <v/>
       </c>
-      <c r="C14" s="74">
+      <c r="C14" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$14),IF('ChartData'!$B$14&lt;=5,'ChartData'!$B$14,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D14" s="74">
+      <c r="D14" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$14),IF(AND('ChartData'!$B$14&gt;5,'ChartData'!$B$14&lt;=10),'ChartData'!$B$14,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E14" s="74">
+      <c r="E14" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$14),IF('ChartData'!$B$14&gt;10,'ChartData'!$B$14,NA()),NA())</f>
         <v/>
       </c>
@@ -8151,15 +8277,15 @@
         <f>IF('Results'!$B$16="","",'Results'!$B$16)</f>
         <v/>
       </c>
-      <c r="C15" s="74">
+      <c r="C15" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$15),IF('ChartData'!$B$15&lt;=5,'ChartData'!$B$15,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D15" s="74">
+      <c r="D15" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$15),IF(AND('ChartData'!$B$15&gt;5,'ChartData'!$B$15&lt;=10),'ChartData'!$B$15,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$15),IF('ChartData'!$B$15&gt;10,'ChartData'!$B$15,NA()),NA())</f>
         <v/>
       </c>
@@ -8174,15 +8300,15 @@
         <f>IF('Results'!$B$17="","",'Results'!$B$17)</f>
         <v/>
       </c>
-      <c r="C16" s="74">
+      <c r="C16" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$16),IF('ChartData'!$B$16&lt;=5,'ChartData'!$B$16,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D16" s="74">
+      <c r="D16" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$16),IF(AND('ChartData'!$B$16&gt;5,'ChartData'!$B$16&lt;=10),'ChartData'!$B$16,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E16" s="74">
+      <c r="E16" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$16),IF('ChartData'!$B$16&gt;10,'ChartData'!$B$16,NA()),NA())</f>
         <v/>
       </c>
@@ -8197,15 +8323,15 @@
         <f>IF('Results'!$B$18="","",'Results'!$B$18)</f>
         <v/>
       </c>
-      <c r="C17" s="74">
+      <c r="C17" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$17),IF('ChartData'!$B$17&lt;=5,'ChartData'!$B$17,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D17" s="74">
+      <c r="D17" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$17),IF(AND('ChartData'!$B$17&gt;5,'ChartData'!$B$17&lt;=10),'ChartData'!$B$17,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E17" s="74">
+      <c r="E17" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$17),IF('ChartData'!$B$17&gt;10,'ChartData'!$B$17,NA()),NA())</f>
         <v/>
       </c>
@@ -8220,41 +8346,41 @@
         <f>IF('Results'!$B$19="","",'Results'!$B$19)</f>
         <v/>
       </c>
-      <c r="C18" s="74">
+      <c r="C18" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$18),IF('ChartData'!$B$18&lt;=5,'ChartData'!$B$18,NA()),NA())</f>
         <v/>
       </c>
-      <c r="D18" s="74">
+      <c r="D18" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$18),IF(AND('ChartData'!$B$18&gt;5,'ChartData'!$B$18&lt;=10),'ChartData'!$B$18,NA()),NA())</f>
         <v/>
       </c>
-      <c r="E18" s="74">
+      <c r="E18" s="75">
         <f>IF(ISNUMBER('ChartData'!$B$18),IF('ChartData'!$B$18&gt;10,'ChartData'!$B$18,NA()),NA())</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="61" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="B20" s="62" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="C20" s="61" t="inlineStr">
+      <c r="C20" s="62" t="inlineStr">
         <is>
           <t>Non-Functioning (0.00-0.39)</t>
         </is>
       </c>
-      <c r="D20" s="61" t="inlineStr">
+      <c r="D20" s="62" t="inlineStr">
         <is>
           <t>Functioning At-Risk (0.40-0.69)</t>
         </is>
       </c>
-      <c r="E20" s="61" t="inlineStr">
+      <c r="E20" s="62" t="inlineStr">
         <is>
           <t>Functioning (0.70-1.00)</t>
         </is>
@@ -8270,15 +8396,15 @@
         <f>'Results'!$B$22</f>
         <v/>
       </c>
-      <c r="C21" s="75">
+      <c r="C21" s="76">
         <f>IF('ChartData'!$B$21&lt;=0.39,'ChartData'!$B$21,NA())</f>
         <v/>
       </c>
-      <c r="D21" s="75">
+      <c r="D21" s="76">
         <f>IF(AND('ChartData'!$B$21&gt;0.39,'ChartData'!$B$21&lt;=0.69),'ChartData'!$B$21,NA())</f>
         <v/>
       </c>
-      <c r="E21" s="75">
+      <c r="E21" s="76">
         <f>IF('ChartData'!$B$21&gt;0.69,'ChartData'!$B$21,NA())</f>
         <v/>
       </c>
@@ -8293,15 +8419,15 @@
         <f>'Results'!$B$23</f>
         <v/>
       </c>
-      <c r="C22" s="75">
+      <c r="C22" s="76">
         <f>IF('ChartData'!$B$22&lt;=0.39,'ChartData'!$B$22,NA())</f>
         <v/>
       </c>
-      <c r="D22" s="75">
+      <c r="D22" s="76">
         <f>IF(AND('ChartData'!$B$22&gt;0.39,'ChartData'!$B$22&lt;=0.69),'ChartData'!$B$22,NA())</f>
         <v/>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="76">
         <f>IF('ChartData'!$B$22&gt;0.69,'ChartData'!$B$22,NA())</f>
         <v/>
       </c>
@@ -8316,15 +8442,15 @@
         <f>'Results'!$B$24</f>
         <v/>
       </c>
-      <c r="C23" s="75">
+      <c r="C23" s="76">
         <f>IF('ChartData'!$B$23&lt;=0.39,'ChartData'!$B$23,NA())</f>
         <v/>
       </c>
-      <c r="D23" s="75">
+      <c r="D23" s="76">
         <f>IF(AND('ChartData'!$B$23&gt;0.39,'ChartData'!$B$23&lt;=0.69),'ChartData'!$B$23,NA())</f>
         <v/>
       </c>
-      <c r="E23" s="75">
+      <c r="E23" s="76">
         <f>IF('ChartData'!$B$23&gt;0.69,'ChartData'!$B$23,NA())</f>
         <v/>
       </c>
@@ -8332,5 +8458,13 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/apps/deep/www/calculators/eastern-corn-belt-plains@v6.xlsx
+++ b/apps/deep/www/calculators/eastern-corn-belt-plains@v6.xlsx
@@ -1517,7 +1517,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -1657,7 +1657,7 @@
     <row r="4" ht="21" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -3054,7 +3054,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -5939,7 +5939,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -5983,7 +5983,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -7725,7 +7725,7 @@
     <row r="2" ht="21" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -8459,7 +8459,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
